--- a/public/resources/BUDGET - Entreprise.xlsx
+++ b/public/resources/BUDGET - Entreprise.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adsgestionca.sharepoint.com/sites/AudreyJames/Shared Documents/Organisateur dépense/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adsgestionca.sharepoint.com/sites/QUIPE-AudreyDroletSamson/Documents partages/Template - fichiers maîtres/Organisateur dépense - Budget/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="371" documentId="8_{13F3CCF0-BCA8-4CC1-8B2A-DF0FF2FCD021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B959943-5DEA-4E33-A13B-50012C58C32C}"/>
+  <xr:revisionPtr revIDLastSave="491" documentId="8_{13F3CCF0-BCA8-4CC1-8B2A-DF0FF2FCD021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E39F1B10-603F-2B43-ADDB-FEE034496344}"/>
   <bookViews>
-    <workbookView xWindow="36680" yWindow="5820" windowWidth="23260" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget - Entreprise" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Revenus générés par la </t>
         </r>
@@ -60,7 +59,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>vente d’articles physiques</t>
         </r>
@@ -70,7 +68,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve"> fabriqués, transformés ou revendus par l’entreprise.</t>
         </r>
@@ -84,13 +81,12 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>accessoires, pièces détachées, emballages premium, etc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{97E8145A-46B6-064D-8E3C-33921CE01B85}">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{97E8145A-46B6-064D-8E3C-33921CE01B85}">
       <text>
         <r>
           <rPr>
@@ -122,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{CB79E463-708E-1F44-84C2-72BFD909F8A7}">
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{CB79E463-708E-1F44-84C2-72BFD909F8A7}">
       <text>
         <r>
           <rPr>
@@ -136,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{724E4A44-1D72-0148-9CBB-51F6BB2FFE26}">
+    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{724E4A44-1D72-0148-9CBB-51F6BB2FFE26}">
       <text>
         <r>
           <rPr>
@@ -168,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{12535CBB-2FBD-0841-87E8-5F879E5BE74B}">
+    <comment ref="B21" authorId="0" shapeId="0" xr:uid="{12535CBB-2FBD-0841-87E8-5F879E5BE74B}">
       <text>
         <r>
           <rPr>
@@ -176,13 +172,12 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>box mensuelles, logiciels, programmes</t>
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0" shapeId="0" xr:uid="{9579CC74-C35D-AB44-A904-2C591FE47A70}">
+    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{9579CC74-C35D-AB44-A904-2C591FE47A70}">
       <text>
         <r>
           <rPr>
@@ -190,7 +185,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Toutes les sources de revenus </t>
         </r>
@@ -201,13 +195,12 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>hors activité principale</t>
         </r>
       </text>
     </comment>
-    <comment ref="B24" authorId="0" shapeId="0" xr:uid="{6F3624A3-847C-E74A-95B5-903FEB1FF4C9}">
+    <comment ref="B27" authorId="0" shapeId="0" xr:uid="{6F3624A3-847C-E74A-95B5-903FEB1FF4C9}">
       <text>
         <r>
           <rPr>
@@ -220,7 +213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{920ED8B9-F02D-DD48-8123-0AF90736CFD4}">
+    <comment ref="B28" authorId="0" shapeId="0" xr:uid="{920ED8B9-F02D-DD48-8123-0AF90736CFD4}">
       <text>
         <r>
           <rPr>
@@ -234,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B26" authorId="0" shapeId="0" xr:uid="{0D4BDFF4-3776-B44B-AAC9-CA09E654F63C}">
+    <comment ref="B29" authorId="0" shapeId="0" xr:uid="{0D4BDFF4-3776-B44B-AAC9-CA09E654F63C}">
       <text>
         <r>
           <rPr>
@@ -242,13 +235,12 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>vente d’actifs, placements, plus-values</t>
         </r>
       </text>
     </comment>
-    <comment ref="B27" authorId="0" shapeId="0" xr:uid="{BA5B91ED-83B5-4B45-B8CD-168C26652075}">
+    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{BA5B91ED-83B5-4B45-B8CD-168C26652075}">
       <text>
         <r>
           <rPr>
@@ -256,13 +248,12 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>vente de matériel, indemnités, partenariats ponctuels</t>
         </r>
       </text>
     </comment>
-    <comment ref="B32" authorId="0" shapeId="0" xr:uid="{7A643713-CC8B-054E-83CC-B43AE540D60B}">
+    <comment ref="B36" authorId="0" shapeId="0" xr:uid="{7A643713-CC8B-054E-83CC-B43AE540D60B}">
       <text>
         <r>
           <rPr>
@@ -271,7 +262,6 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Coût de revient
 </t>
@@ -282,14 +272,13 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">Dépenses directement liées à la production ou à la vente des biens et services
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="B40" authorId="0" shapeId="0" xr:uid="{2B7B7E0E-DD1F-CC40-BB06-23588A3ED143}">
+    <comment ref="B45" authorId="0" shapeId="0" xr:uid="{2B7B7E0E-DD1F-CC40-BB06-23588A3ED143}">
       <text>
         <r>
           <rPr>
@@ -303,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B76" authorId="0" shapeId="0" xr:uid="{65BC69C0-4181-9547-BA04-8854D15E1EFE}">
+    <comment ref="B86" authorId="0" shapeId="0" xr:uid="{65BC69C0-4181-9547-BA04-8854D15E1EFE}">
       <text>
         <r>
           <rPr>
@@ -316,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B90" authorId="0" shapeId="0" xr:uid="{0EAC4B7E-5EAD-2946-B900-F060F511F151}">
+    <comment ref="B102" authorId="0" shapeId="0" xr:uid="{0EAC4B7E-5EAD-2946-B900-F060F511F151}">
       <text>
         <r>
           <rPr>
@@ -357,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="103">
   <si>
     <t>Revenus</t>
   </si>
@@ -404,9 +393,6 @@
     <t>Ventes de produits :</t>
   </si>
   <si>
-    <t xml:space="preserve">Total : </t>
-  </si>
-  <si>
     <t>Produits fabriqués par l’entreprise</t>
   </si>
   <si>
@@ -630,6 +616,45 @@
   </si>
   <si>
     <t>Dépenses totales</t>
+  </si>
+  <si>
+    <t>Total abonnements / contrats récurrents :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total autres revenus : </t>
+  </si>
+  <si>
+    <t>Total ventes de services :</t>
+  </si>
+  <si>
+    <t>Total ventes de produits :</t>
+  </si>
+  <si>
+    <t>Total coûts liés aux ventes / production :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total salaires et chages sociales : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total loyer et charges d'occupation : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total équipements et maintenance : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total marketing et publicité : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total frais administratifs : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total déplacements et représentation : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total assurances et protections : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total impôts et taxes : </t>
   </si>
 </sst>
 </file>
@@ -640,7 +665,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;$&quot;"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ \ [$$-C0C]_ ;_ * \-#,##0.00\ \ [$$-C0C]_ ;_ * &quot;-&quot;??_ \ [$$-C0C]_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -742,14 +767,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Display"/>
@@ -773,8 +790,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -809,12 +832,27 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1AE93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -824,7 +862,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -906,18 +944,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="14" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -926,7 +958,7 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -935,14 +967,21 @@
     <xf numFmtId="165" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1814,9 +1853,10 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FF456882"/>
+      <color rgb="FFC1AE93"/>
+      <color rgb="FFD2C1B6"/>
       <color rgb="FFFFFCF8"/>
-      <color rgb="FFD2C1B6"/>
-      <color rgb="FF456882"/>
       <color rgb="FFC0C3B2"/>
       <color rgb="FF483729"/>
     </mruColors>
@@ -1897,8 +1937,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13C5FA62-0D39-C146-966B-D9A3B9A0EA83}" name="income" displayName="income" ref="B2:O29" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" headerRowCellStyle="Accent5">
-  <autoFilter ref="B2:O29" xr:uid="{13C5FA62-0D39-C146-966B-D9A3B9A0EA83}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13C5FA62-0D39-C146-966B-D9A3B9A0EA83}" name="income" displayName="income" ref="B2:O33" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" headerRowCellStyle="Accent5">
+  <autoFilter ref="B2:O33" xr:uid="{13C5FA62-0D39-C146-966B-D9A3B9A0EA83}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1935,8 +1975,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B66D6E5F-B806-0F42-BF93-C697A3628B74}" name="outcomes" displayName="outcomes" ref="B31:O92" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowCellStyle="Accent5">
-  <autoFilter ref="B31:O92" xr:uid="{B66D6E5F-B806-0F42-BF93-C697A3628B74}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B66D6E5F-B806-0F42-BF93-C697A3628B74}" name="outcomes" displayName="outcomes" ref="B35:O105" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowCellStyle="Accent5">
+  <autoFilter ref="B35:O105" xr:uid="{B66D6E5F-B806-0F42-BF93-C697A3628B74}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2238,25 +2278,25 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:DM98"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="B1:DM111"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="2" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="3" customWidth="1"/>
-    <col min="5" max="10" width="11.28515625" style="3" customWidth="1"/>
-    <col min="11" max="14" width="12.28515625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="2" width="53.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" style="3" customWidth="1"/>
+    <col min="5" max="10" width="11.33203125" style="3" customWidth="1"/>
+    <col min="11" max="14" width="12.33203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="12.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="67.349999999999994" customHeight="1">
+    <row r="1" spans="2:15" ht="67.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="2:15" s="4" customFormat="1" ht="27" customHeight="1">
+    <row r="2" spans="2:15" s="4" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -2300,7 +2340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:15" s="4" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="3" spans="2:15" s="4" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="30" t="s">
         <v>14</v>
       </c>
@@ -2315,17 +2355,12 @@
       <c r="K3" s="29"/>
       <c r="L3" s="29"/>
       <c r="M3" s="29"/>
-      <c r="N3" s="29" t="s">
+      <c r="N3" s="29"/>
+      <c r="O3" s="28"/>
+    </row>
+    <row r="4" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="O3" s="28">
-        <f>SUM(O4:O9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B4" s="8" t="s">
-        <v>16</v>
       </c>
       <c r="C4" s="9">
         <v>0</v>
@@ -2368,9 +2403,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="17.100000000000001" customHeight="1">
+    <row r="5" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="9">
         <v>0</v>
@@ -2413,9 +2448,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="17.100000000000001" customHeight="1">
+    <row r="6" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -2458,9 +2493,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="17.100000000000001" customHeight="1">
+    <row r="7" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="9">
         <v>0</v>
@@ -2503,9 +2538,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:15" ht="17.100000000000001" customHeight="1">
+    <row r="8" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -2548,93 +2583,127 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="32"/>
-    </row>
-    <row r="10" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B10" s="26" t="s">
+    <row r="9" spans="2:15" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="42"/>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10">
+        <f t="shared" ref="O9" si="2">SUM(C9:N9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="44">
+        <f>SUM(C4:C9)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="44">
+        <f t="shared" ref="D10:N10" si="3">SUM(D4:D9)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="44">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="44">
+        <f>SUM(O4:O9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="28"/>
+    </row>
+    <row r="12" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="8" t="s">
         <v>21</v>
-      </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O10" s="28">
-        <f>SUM(O11:O15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>0</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9">
-        <v>0</v>
-      </c>
-      <c r="N11" s="9">
-        <v>0</v>
-      </c>
-      <c r="O11" s="10">
-        <f>SUM(C11:N11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B12" s="8" t="s">
-        <v>23</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
@@ -2677,9 +2746,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:15" ht="17.100000000000001" customHeight="1">
+    <row r="13" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="9">
         <v>0</v>
@@ -2722,9 +2791,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="17.100000000000001" customHeight="1">
+    <row r="14" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" s="9">
         <v>0</v>
@@ -2767,138 +2836,172 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="32"/>
-    </row>
-    <row r="16" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B16" s="26" t="s">
+    <row r="15" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
+        <f>SUM(C15:N15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="42"/>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
+        <f>SUM(C16:N16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="44">
+        <f>SUM(C12:C16)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="44">
+        <f t="shared" ref="D17:O17" si="4">SUM(D12:D16)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="44">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="28"/>
+    </row>
+    <row r="19" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O16" s="28">
-        <f>SUM(O17:O21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="9">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0</v>
-      </c>
-      <c r="F17" s="9">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>0</v>
-      </c>
-      <c r="I17" s="9">
-        <v>0</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9">
-        <v>0</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9">
-        <v>0</v>
-      </c>
-      <c r="N17" s="9">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10">
-        <f>SUM(C17:N17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="9">
-        <v>0</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9">
-        <v>0</v>
-      </c>
-      <c r="F18" s="9">
-        <v>0</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0</v>
-      </c>
-      <c r="I18" s="9">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9">
-        <v>0</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9">
-        <v>0</v>
-      </c>
-      <c r="O18" s="10">
-        <f>SUM(C18:N18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B19" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="C19" s="9">
         <v>0</v>
@@ -2941,9 +3044,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:15" ht="17.100000000000001" customHeight="1">
+    <row r="20" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C20" s="9">
         <v>0</v>
@@ -2986,2377 +3089,2614 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="10"/>
-    </row>
-    <row r="22" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B22" s="26" t="s">
+    <row r="21" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10">
+        <f>SUM(C21:N21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+      <c r="O22" s="10">
+        <f>SUM(C22:N22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="42"/>
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10">
+        <f>SUM(C23:N23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="44">
+        <f>SUM(C19:C23)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="44">
+        <f t="shared" ref="D24" si="5">SUM(D19:D23)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="44">
+        <f t="shared" ref="E24" si="6">SUM(E19:E23)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="44">
+        <f t="shared" ref="F24" si="7">SUM(F19:F23)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="44">
+        <f t="shared" ref="G24" si="8">SUM(G19:G23)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="44">
+        <f t="shared" ref="H24" si="9">SUM(H19:H23)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="44">
+        <f t="shared" ref="I24" si="10">SUM(I19:I23)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="44">
+        <f t="shared" ref="J24" si="11">SUM(J19:J23)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="44">
+        <f t="shared" ref="K24" si="12">SUM(K19:K23)</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="44">
+        <f t="shared" ref="L24" si="13">SUM(L19:L23)</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="44">
+        <f t="shared" ref="M24" si="14">SUM(M19:M23)</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="44">
+        <f t="shared" ref="N24" si="15">SUM(N19:N23)</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="44">
+        <f t="shared" ref="O24" si="16">SUM(O19:O23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="28"/>
+    </row>
+    <row r="26" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O22" s="28">
-        <f>SUM(O23:O28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B23" s="8" t="s">
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0</v>
+      </c>
+      <c r="O26" s="10">
+        <f t="shared" ref="O26:O27" si="17">SUM(C26:N26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="9">
-        <v>0</v>
-      </c>
-      <c r="D23" s="9">
-        <v>0</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>0</v>
-      </c>
-      <c r="I23" s="9">
-        <v>0</v>
-      </c>
-      <c r="J23" s="9">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9">
-        <v>0</v>
-      </c>
-      <c r="L23" s="9">
-        <v>0</v>
-      </c>
-      <c r="M23" s="9">
-        <v>0</v>
-      </c>
-      <c r="N23" s="9">
-        <v>0</v>
-      </c>
-      <c r="O23" s="10">
-        <f t="shared" ref="O23:O24" si="2">SUM(C23:N23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B24" s="8" t="s">
+      <c r="C27" s="9">
+        <v>0</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0</v>
+      </c>
+      <c r="J27" s="9">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9">
+        <v>0</v>
+      </c>
+      <c r="M27" s="9">
+        <v>0</v>
+      </c>
+      <c r="N27" s="9">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="9">
-        <v>0</v>
-      </c>
-      <c r="D24" s="9">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>0</v>
-      </c>
-      <c r="I24" s="9">
-        <v>0</v>
-      </c>
-      <c r="J24" s="9">
-        <v>0</v>
-      </c>
-      <c r="K24" s="9">
-        <v>0</v>
-      </c>
-      <c r="L24" s="9">
-        <v>0</v>
-      </c>
-      <c r="M24" s="9">
-        <v>0</v>
-      </c>
-      <c r="N24" s="9">
-        <v>0</v>
-      </c>
-      <c r="O24" s="10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B25" s="8" t="s">
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="9">
+        <v>0</v>
+      </c>
+      <c r="J28" s="9">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9">
+        <v>0</v>
+      </c>
+      <c r="M28" s="9">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9">
+        <v>0</v>
+      </c>
+      <c r="O28" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" s="11" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="9">
-        <v>0</v>
-      </c>
-      <c r="D25" s="9">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>0</v>
-      </c>
-      <c r="I25" s="9">
-        <v>0</v>
-      </c>
-      <c r="J25" s="9">
-        <v>0</v>
-      </c>
-      <c r="K25" s="9">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9">
-        <v>0</v>
-      </c>
-      <c r="M25" s="9">
-        <v>0</v>
-      </c>
-      <c r="N25" s="9">
-        <v>0</v>
-      </c>
-      <c r="O25" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B26" s="8" t="s">
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>0</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0</v>
+      </c>
+      <c r="J29" s="9">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9">
+        <v>0</v>
+      </c>
+      <c r="M29" s="9">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9">
+        <v>0</v>
+      </c>
+      <c r="O29" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" s="11" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="9">
-        <v>0</v>
-      </c>
-      <c r="D26" s="9">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0</v>
-      </c>
-      <c r="F26" s="9">
-        <v>0</v>
-      </c>
-      <c r="G26" s="9">
-        <v>0</v>
-      </c>
-      <c r="H26" s="9">
-        <v>0</v>
-      </c>
-      <c r="I26" s="9">
-        <v>0</v>
-      </c>
-      <c r="J26" s="9">
-        <v>0</v>
-      </c>
-      <c r="K26" s="9">
-        <v>0</v>
-      </c>
-      <c r="L26" s="9">
-        <v>0</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0</v>
-      </c>
-      <c r="N26" s="9">
-        <v>0</v>
-      </c>
-      <c r="O26" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B27" s="8" t="s">
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+      <c r="J30" s="9">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9">
+        <v>0</v>
+      </c>
+      <c r="M30" s="9">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9">
+        <v>0</v>
+      </c>
+      <c r="O30" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" s="11" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="42"/>
+      <c r="C31" s="9">
+        <v>0</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>0</v>
+      </c>
+      <c r="I31" s="9">
+        <v>0</v>
+      </c>
+      <c r="J31" s="9">
+        <v>0</v>
+      </c>
+      <c r="K31" s="9">
+        <v>0</v>
+      </c>
+      <c r="L31" s="9">
+        <v>0</v>
+      </c>
+      <c r="M31" s="9">
+        <v>0</v>
+      </c>
+      <c r="N31" s="9">
+        <v>0</v>
+      </c>
+      <c r="O31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" s="11" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="44">
+        <f>SUM(C26:C31)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="44">
+        <f t="shared" ref="D32:O32" si="18">SUM(D26:D31)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O32" s="44">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" s="15" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="9">
-        <v>0</v>
-      </c>
-      <c r="D27" s="9">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9">
-        <v>0</v>
-      </c>
-      <c r="F27" s="9">
-        <v>0</v>
-      </c>
-      <c r="G27" s="9">
-        <v>0</v>
-      </c>
-      <c r="H27" s="9">
-        <v>0</v>
-      </c>
-      <c r="I27" s="9">
-        <v>0</v>
-      </c>
-      <c r="J27" s="9">
-        <v>0</v>
-      </c>
-      <c r="K27" s="9">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9">
-        <v>0</v>
-      </c>
-      <c r="M27" s="9">
-        <v>0</v>
-      </c>
-      <c r="N27" s="9">
-        <v>0</v>
-      </c>
-      <c r="O27" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" ht="17.100000000000001" customHeight="1">
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="10"/>
-    </row>
-    <row r="29" spans="2:15" s="11" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B29" s="12" t="s">
+      <c r="C33" s="13">
+        <f>SUM(C4:C9,C12:C16,C19:C23,C26:C31)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="13">
+        <f t="shared" ref="D33:N33" si="19">SUM(D4:D9,D12:D16,D19:D23,D26:D31)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="13">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="37">
+        <f>SUM(income[[#This Row],[Janvier]:[Déc]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" s="15" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="40"/>
+    </row>
+    <row r="35" spans="2:15" s="15" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="13">
-        <f t="shared" ref="C29:N29" si="3">SUM(C4:C27)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="39">
-        <f>SUM(income[[#This Row],[Janvier]:[Déc]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" s="11" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="42"/>
-    </row>
-    <row r="31" spans="2:15" s="11" customFormat="1" ht="28.35" customHeight="1">
-      <c r="B31" s="14" t="s">
+      <c r="C35" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N31" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O31" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B32" s="16" t="s">
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="21"/>
+    </row>
+    <row r="37" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O32" s="21">
-        <f>SUM(O33:O37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B33" s="19" t="s">
+      <c r="C37" s="20">
+        <v>0</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0</v>
+      </c>
+      <c r="F37" s="20">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0</v>
+      </c>
+      <c r="H37" s="20">
+        <v>0</v>
+      </c>
+      <c r="I37" s="20">
+        <v>0</v>
+      </c>
+      <c r="J37" s="20">
+        <v>0</v>
+      </c>
+      <c r="K37" s="20">
+        <v>0</v>
+      </c>
+      <c r="L37" s="20">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20">
+        <v>0</v>
+      </c>
+      <c r="N37" s="20">
+        <v>0</v>
+      </c>
+      <c r="O37" s="32">
+        <f t="shared" ref="O37:O52" si="20">SUM(C37:N37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="20">
-        <v>0</v>
-      </c>
-      <c r="D33" s="20">
-        <v>0</v>
-      </c>
-      <c r="E33" s="20">
-        <v>0</v>
-      </c>
-      <c r="F33" s="20">
-        <v>0</v>
-      </c>
-      <c r="G33" s="20">
-        <v>0</v>
-      </c>
-      <c r="H33" s="20">
-        <v>0</v>
-      </c>
-      <c r="I33" s="20">
-        <v>0</v>
-      </c>
-      <c r="J33" s="20">
-        <v>0</v>
-      </c>
-      <c r="K33" s="20">
-        <v>0</v>
-      </c>
-      <c r="L33" s="20">
-        <v>0</v>
-      </c>
-      <c r="M33" s="20">
-        <v>0</v>
-      </c>
-      <c r="N33" s="20">
-        <v>0</v>
-      </c>
-      <c r="O33" s="33">
-        <f t="shared" ref="O33:O46" si="4">SUM(C33:N33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B34" s="19" t="s">
+      <c r="C38" s="20">
+        <v>0</v>
+      </c>
+      <c r="D38" s="20">
+        <v>0</v>
+      </c>
+      <c r="E38" s="20">
+        <v>0</v>
+      </c>
+      <c r="F38" s="20">
+        <v>0</v>
+      </c>
+      <c r="G38" s="20">
+        <v>0</v>
+      </c>
+      <c r="H38" s="20">
+        <v>0</v>
+      </c>
+      <c r="I38" s="20">
+        <v>0</v>
+      </c>
+      <c r="J38" s="20">
+        <v>0</v>
+      </c>
+      <c r="K38" s="20">
+        <v>0</v>
+      </c>
+      <c r="L38" s="20">
+        <v>0</v>
+      </c>
+      <c r="M38" s="20">
+        <v>0</v>
+      </c>
+      <c r="N38" s="20">
+        <v>0</v>
+      </c>
+      <c r="O38" s="32">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="20">
-        <v>0</v>
-      </c>
-      <c r="D34" s="20">
-        <v>0</v>
-      </c>
-      <c r="E34" s="20">
-        <v>0</v>
-      </c>
-      <c r="F34" s="20">
-        <v>0</v>
-      </c>
-      <c r="G34" s="20">
-        <v>0</v>
-      </c>
-      <c r="H34" s="20">
-        <v>0</v>
-      </c>
-      <c r="I34" s="20">
-        <v>0</v>
-      </c>
-      <c r="J34" s="20">
-        <v>0</v>
-      </c>
-      <c r="K34" s="20">
-        <v>0</v>
-      </c>
-      <c r="L34" s="20">
-        <v>0</v>
-      </c>
-      <c r="M34" s="20">
-        <v>0</v>
-      </c>
-      <c r="N34" s="20">
-        <v>0</v>
-      </c>
-      <c r="O34" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B35" s="19" t="s">
+      <c r="C39" s="20">
+        <v>0</v>
+      </c>
+      <c r="D39" s="20">
+        <v>0</v>
+      </c>
+      <c r="E39" s="20">
+        <v>0</v>
+      </c>
+      <c r="F39" s="20">
+        <v>0</v>
+      </c>
+      <c r="G39" s="20">
+        <v>0</v>
+      </c>
+      <c r="H39" s="20">
+        <v>0</v>
+      </c>
+      <c r="I39" s="20">
+        <v>0</v>
+      </c>
+      <c r="J39" s="20">
+        <v>0</v>
+      </c>
+      <c r="K39" s="20">
+        <v>0</v>
+      </c>
+      <c r="L39" s="20">
+        <v>0</v>
+      </c>
+      <c r="M39" s="20">
+        <v>0</v>
+      </c>
+      <c r="N39" s="20">
+        <v>0</v>
+      </c>
+      <c r="O39" s="32">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="20">
-        <v>0</v>
-      </c>
-      <c r="D35" s="20">
-        <v>0</v>
-      </c>
-      <c r="E35" s="20">
-        <v>0</v>
-      </c>
-      <c r="F35" s="20">
-        <v>0</v>
-      </c>
-      <c r="G35" s="20">
-        <v>0</v>
-      </c>
-      <c r="H35" s="20">
-        <v>0</v>
-      </c>
-      <c r="I35" s="20">
-        <v>0</v>
-      </c>
-      <c r="J35" s="20">
-        <v>0</v>
-      </c>
-      <c r="K35" s="20">
-        <v>0</v>
-      </c>
-      <c r="L35" s="20">
-        <v>0</v>
-      </c>
-      <c r="M35" s="20">
-        <v>0</v>
-      </c>
-      <c r="N35" s="20">
-        <v>0</v>
-      </c>
-      <c r="O35" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B36" s="19" t="s">
+      <c r="C40" s="20">
+        <v>0</v>
+      </c>
+      <c r="D40" s="20">
+        <v>0</v>
+      </c>
+      <c r="E40" s="20">
+        <v>0</v>
+      </c>
+      <c r="F40" s="20">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20">
+        <v>0</v>
+      </c>
+      <c r="H40" s="20">
+        <v>0</v>
+      </c>
+      <c r="I40" s="20">
+        <v>0</v>
+      </c>
+      <c r="J40" s="20">
+        <v>0</v>
+      </c>
+      <c r="K40" s="20">
+        <v>0</v>
+      </c>
+      <c r="L40" s="20">
+        <v>0</v>
+      </c>
+      <c r="M40" s="20">
+        <v>0</v>
+      </c>
+      <c r="N40" s="20">
+        <v>0</v>
+      </c>
+      <c r="O40" s="32">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="45"/>
+      <c r="C41" s="20">
+        <v>0</v>
+      </c>
+      <c r="D41" s="20">
+        <v>0</v>
+      </c>
+      <c r="E41" s="20">
+        <v>0</v>
+      </c>
+      <c r="F41" s="20">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20">
+        <v>0</v>
+      </c>
+      <c r="H41" s="20">
+        <v>0</v>
+      </c>
+      <c r="I41" s="20">
+        <v>0</v>
+      </c>
+      <c r="J41" s="20">
+        <v>0</v>
+      </c>
+      <c r="K41" s="20">
+        <v>0</v>
+      </c>
+      <c r="L41" s="20">
+        <v>0</v>
+      </c>
+      <c r="M41" s="20">
+        <v>0</v>
+      </c>
+      <c r="N41" s="20">
+        <v>0</v>
+      </c>
+      <c r="O41" s="32">
+        <f t="shared" ref="O41" si="21">SUM(C41:N41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="44">
+        <f>SUM(C37:C41)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="44">
+        <f t="shared" ref="D42:N42" si="22">SUM(D37:D41)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="G42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="44">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="O42" s="44">
+        <f>SUM(O37:O41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="20">
-        <v>0</v>
-      </c>
-      <c r="D36" s="20">
-        <v>0</v>
-      </c>
-      <c r="E36" s="20">
-        <v>0</v>
-      </c>
-      <c r="F36" s="20">
-        <v>0</v>
-      </c>
-      <c r="G36" s="20">
-        <v>0</v>
-      </c>
-      <c r="H36" s="20">
-        <v>0</v>
-      </c>
-      <c r="I36" s="20">
-        <v>0</v>
-      </c>
-      <c r="J36" s="20">
-        <v>0</v>
-      </c>
-      <c r="K36" s="20">
-        <v>0</v>
-      </c>
-      <c r="L36" s="20">
-        <v>0</v>
-      </c>
-      <c r="M36" s="20">
-        <v>0</v>
-      </c>
-      <c r="N36" s="20">
-        <v>0</v>
-      </c>
-      <c r="O36" s="33">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B37" s="19"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="18"/>
-    </row>
-    <row r="38" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B38" s="16" t="s">
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="21"/>
+    </row>
+    <row r="44" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O38" s="21">
-        <f>SUM(O39:O43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B39" s="19" t="s">
+      <c r="C44" s="20">
+        <v>0</v>
+      </c>
+      <c r="D44" s="20">
+        <v>0</v>
+      </c>
+      <c r="E44" s="20">
+        <v>0</v>
+      </c>
+      <c r="F44" s="20">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20">
+        <v>0</v>
+      </c>
+      <c r="H44" s="20">
+        <v>0</v>
+      </c>
+      <c r="I44" s="20">
+        <v>0</v>
+      </c>
+      <c r="J44" s="20">
+        <v>0</v>
+      </c>
+      <c r="K44" s="20">
+        <v>0</v>
+      </c>
+      <c r="L44" s="20">
+        <v>0</v>
+      </c>
+      <c r="M44" s="20">
+        <v>0</v>
+      </c>
+      <c r="N44" s="20">
+        <v>0</v>
+      </c>
+      <c r="O44" s="18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="20">
-        <v>0</v>
-      </c>
-      <c r="D39" s="20">
-        <v>0</v>
-      </c>
-      <c r="E39" s="20">
-        <v>0</v>
-      </c>
-      <c r="F39" s="20">
-        <v>0</v>
-      </c>
-      <c r="G39" s="20">
-        <v>0</v>
-      </c>
-      <c r="H39" s="20">
-        <v>0</v>
-      </c>
-      <c r="I39" s="20">
-        <v>0</v>
-      </c>
-      <c r="J39" s="20">
-        <v>0</v>
-      </c>
-      <c r="K39" s="20">
-        <v>0</v>
-      </c>
-      <c r="L39" s="20">
-        <v>0</v>
-      </c>
-      <c r="M39" s="20">
-        <v>0</v>
-      </c>
-      <c r="N39" s="20">
-        <v>0</v>
-      </c>
-      <c r="O39" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B40" s="19" t="s">
+      <c r="C45" s="20">
+        <v>0</v>
+      </c>
+      <c r="D45" s="20">
+        <v>0</v>
+      </c>
+      <c r="E45" s="20">
+        <v>0</v>
+      </c>
+      <c r="F45" s="20">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20">
+        <v>0</v>
+      </c>
+      <c r="H45" s="20">
+        <v>0</v>
+      </c>
+      <c r="I45" s="20">
+        <v>0</v>
+      </c>
+      <c r="J45" s="20">
+        <v>0</v>
+      </c>
+      <c r="K45" s="20">
+        <v>0</v>
+      </c>
+      <c r="L45" s="20">
+        <v>0</v>
+      </c>
+      <c r="M45" s="20">
+        <v>0</v>
+      </c>
+      <c r="N45" s="20">
+        <v>0</v>
+      </c>
+      <c r="O45" s="18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="20">
-        <v>0</v>
-      </c>
-      <c r="D40" s="20">
-        <v>0</v>
-      </c>
-      <c r="E40" s="20">
-        <v>0</v>
-      </c>
-      <c r="F40" s="20">
-        <v>0</v>
-      </c>
-      <c r="G40" s="20">
-        <v>0</v>
-      </c>
-      <c r="H40" s="20">
-        <v>0</v>
-      </c>
-      <c r="I40" s="20">
-        <v>0</v>
-      </c>
-      <c r="J40" s="20">
-        <v>0</v>
-      </c>
-      <c r="K40" s="20">
-        <v>0</v>
-      </c>
-      <c r="L40" s="20">
-        <v>0</v>
-      </c>
-      <c r="M40" s="20">
-        <v>0</v>
-      </c>
-      <c r="N40" s="20">
-        <v>0</v>
-      </c>
-      <c r="O40" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B41" s="19" t="s">
+      <c r="C46" s="20">
+        <v>0</v>
+      </c>
+      <c r="D46" s="20">
+        <v>0</v>
+      </c>
+      <c r="E46" s="20">
+        <v>0</v>
+      </c>
+      <c r="F46" s="20">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20">
+        <v>0</v>
+      </c>
+      <c r="H46" s="20">
+        <v>0</v>
+      </c>
+      <c r="I46" s="20">
+        <v>0</v>
+      </c>
+      <c r="J46" s="20">
+        <v>0</v>
+      </c>
+      <c r="K46" s="20">
+        <v>0</v>
+      </c>
+      <c r="L46" s="20">
+        <v>0</v>
+      </c>
+      <c r="M46" s="20">
+        <v>0</v>
+      </c>
+      <c r="N46" s="20">
+        <v>0</v>
+      </c>
+      <c r="O46" s="18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="20">
-        <v>0</v>
-      </c>
-      <c r="D41" s="20">
-        <v>0</v>
-      </c>
-      <c r="E41" s="20">
-        <v>0</v>
-      </c>
-      <c r="F41" s="20">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20">
-        <v>0</v>
-      </c>
-      <c r="H41" s="20">
-        <v>0</v>
-      </c>
-      <c r="I41" s="20">
-        <v>0</v>
-      </c>
-      <c r="J41" s="20">
-        <v>0</v>
-      </c>
-      <c r="K41" s="20">
-        <v>0</v>
-      </c>
-      <c r="L41" s="20">
-        <v>0</v>
-      </c>
-      <c r="M41" s="20">
-        <v>0</v>
-      </c>
-      <c r="N41" s="20">
-        <v>0</v>
-      </c>
-      <c r="O41" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B42" s="19" t="s">
+      <c r="C47" s="20">
+        <v>0</v>
+      </c>
+      <c r="D47" s="20">
+        <v>0</v>
+      </c>
+      <c r="E47" s="20">
+        <v>0</v>
+      </c>
+      <c r="F47" s="20">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20">
+        <v>0</v>
+      </c>
+      <c r="H47" s="20">
+        <v>0</v>
+      </c>
+      <c r="I47" s="20">
+        <v>0</v>
+      </c>
+      <c r="J47" s="20">
+        <v>0</v>
+      </c>
+      <c r="K47" s="20">
+        <v>0</v>
+      </c>
+      <c r="L47" s="20">
+        <v>0</v>
+      </c>
+      <c r="M47" s="20">
+        <v>0</v>
+      </c>
+      <c r="N47" s="20">
+        <v>0</v>
+      </c>
+      <c r="O47" s="18">
+        <f t="shared" ref="O47" si="23">SUM(C47:N47)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="45"/>
+      <c r="C48" s="20">
+        <v>0</v>
+      </c>
+      <c r="D48" s="20">
+        <v>0</v>
+      </c>
+      <c r="E48" s="20">
+        <v>0</v>
+      </c>
+      <c r="F48" s="20">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20">
+        <v>0</v>
+      </c>
+      <c r="H48" s="20">
+        <v>0</v>
+      </c>
+      <c r="I48" s="20">
+        <v>0</v>
+      </c>
+      <c r="J48" s="20">
+        <v>0</v>
+      </c>
+      <c r="K48" s="20">
+        <v>0</v>
+      </c>
+      <c r="L48" s="20">
+        <v>0</v>
+      </c>
+      <c r="M48" s="20">
+        <v>0</v>
+      </c>
+      <c r="N48" s="20">
+        <v>0</v>
+      </c>
+      <c r="O48" s="18">
+        <f t="shared" ref="O48" si="24">SUM(C48:N48)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="44">
+        <f>SUM(C44:C48)</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="44">
+        <f t="shared" ref="D49:O49" si="25">SUM(D44:D48)</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="L49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="N49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="44">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="20">
-        <v>0</v>
-      </c>
-      <c r="D42" s="20">
-        <v>0</v>
-      </c>
-      <c r="E42" s="20">
-        <v>0</v>
-      </c>
-      <c r="F42" s="20">
-        <v>0</v>
-      </c>
-      <c r="G42" s="20">
-        <v>0</v>
-      </c>
-      <c r="H42" s="20">
-        <v>0</v>
-      </c>
-      <c r="I42" s="20">
-        <v>0</v>
-      </c>
-      <c r="J42" s="20">
-        <v>0</v>
-      </c>
-      <c r="K42" s="20">
-        <v>0</v>
-      </c>
-      <c r="L42" s="20">
-        <v>0</v>
-      </c>
-      <c r="M42" s="20">
-        <v>0</v>
-      </c>
-      <c r="N42" s="20">
-        <v>0</v>
-      </c>
-      <c r="O42" s="18">
-        <f t="shared" ref="O42" si="5">SUM(C42:N42)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B43" s="19"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="18"/>
-    </row>
-    <row r="44" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B44" s="16" t="s">
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="21"/>
+    </row>
+    <row r="51" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O44" s="21">
-        <f>SUM(O45:O55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B45" s="19" t="s">
+      <c r="C51" s="20">
+        <v>0</v>
+      </c>
+      <c r="D51" s="20">
+        <v>0</v>
+      </c>
+      <c r="E51" s="20">
+        <v>0</v>
+      </c>
+      <c r="F51" s="20">
+        <v>0</v>
+      </c>
+      <c r="G51" s="20">
+        <v>0</v>
+      </c>
+      <c r="H51" s="20">
+        <v>0</v>
+      </c>
+      <c r="I51" s="20">
+        <v>0</v>
+      </c>
+      <c r="J51" s="20">
+        <v>0</v>
+      </c>
+      <c r="K51" s="20">
+        <v>0</v>
+      </c>
+      <c r="L51" s="20">
+        <v>0</v>
+      </c>
+      <c r="M51" s="20">
+        <v>0</v>
+      </c>
+      <c r="N51" s="20">
+        <v>0</v>
+      </c>
+      <c r="O51" s="18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="20">
-        <v>0</v>
-      </c>
-      <c r="D45" s="20">
-        <v>0</v>
-      </c>
-      <c r="E45" s="20">
-        <v>0</v>
-      </c>
-      <c r="F45" s="20">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20">
-        <v>0</v>
-      </c>
-      <c r="H45" s="20">
-        <v>0</v>
-      </c>
-      <c r="I45" s="20">
-        <v>0</v>
-      </c>
-      <c r="J45" s="20">
-        <v>0</v>
-      </c>
-      <c r="K45" s="20">
-        <v>0</v>
-      </c>
-      <c r="L45" s="20">
-        <v>0</v>
-      </c>
-      <c r="M45" s="20">
-        <v>0</v>
-      </c>
-      <c r="N45" s="20">
-        <v>0</v>
-      </c>
-      <c r="O45" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B46" s="19" t="s">
+      <c r="C52" s="20">
+        <v>0</v>
+      </c>
+      <c r="D52" s="20">
+        <v>0</v>
+      </c>
+      <c r="E52" s="20">
+        <v>0</v>
+      </c>
+      <c r="F52" s="20">
+        <v>0</v>
+      </c>
+      <c r="G52" s="20">
+        <v>0</v>
+      </c>
+      <c r="H52" s="20">
+        <v>0</v>
+      </c>
+      <c r="I52" s="20">
+        <v>0</v>
+      </c>
+      <c r="J52" s="20">
+        <v>0</v>
+      </c>
+      <c r="K52" s="20">
+        <v>0</v>
+      </c>
+      <c r="L52" s="20">
+        <v>0</v>
+      </c>
+      <c r="M52" s="20">
+        <v>0</v>
+      </c>
+      <c r="N52" s="20">
+        <v>0</v>
+      </c>
+      <c r="O52" s="18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="20">
-        <v>0</v>
-      </c>
-      <c r="D46" s="20">
-        <v>0</v>
-      </c>
-      <c r="E46" s="20">
-        <v>0</v>
-      </c>
-      <c r="F46" s="20">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20">
-        <v>0</v>
-      </c>
-      <c r="H46" s="20">
-        <v>0</v>
-      </c>
-      <c r="I46" s="20">
-        <v>0</v>
-      </c>
-      <c r="J46" s="20">
-        <v>0</v>
-      </c>
-      <c r="K46" s="20">
-        <v>0</v>
-      </c>
-      <c r="L46" s="20">
-        <v>0</v>
-      </c>
-      <c r="M46" s="20">
-        <v>0</v>
-      </c>
-      <c r="N46" s="20">
-        <v>0</v>
-      </c>
-      <c r="O46" s="18">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B47" s="19" t="s">
+      <c r="C53" s="20">
+        <v>0</v>
+      </c>
+      <c r="D53" s="20">
+        <v>0</v>
+      </c>
+      <c r="E53" s="20">
+        <v>0</v>
+      </c>
+      <c r="F53" s="20">
+        <v>0</v>
+      </c>
+      <c r="G53" s="20">
+        <v>0</v>
+      </c>
+      <c r="H53" s="20">
+        <v>0</v>
+      </c>
+      <c r="I53" s="20">
+        <v>0</v>
+      </c>
+      <c r="J53" s="20">
+        <v>0</v>
+      </c>
+      <c r="K53" s="20">
+        <v>0</v>
+      </c>
+      <c r="L53" s="20">
+        <v>0</v>
+      </c>
+      <c r="M53" s="20">
+        <v>0</v>
+      </c>
+      <c r="N53" s="20">
+        <v>0</v>
+      </c>
+      <c r="O53" s="18">
+        <f t="shared" ref="O53:O60" si="26">SUM(C53:N53)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="20">
-        <v>0</v>
-      </c>
-      <c r="D47" s="20">
-        <v>0</v>
-      </c>
-      <c r="E47" s="20">
-        <v>0</v>
-      </c>
-      <c r="F47" s="20">
-        <v>0</v>
-      </c>
-      <c r="G47" s="20">
-        <v>0</v>
-      </c>
-      <c r="H47" s="20">
-        <v>0</v>
-      </c>
-      <c r="I47" s="20">
-        <v>0</v>
-      </c>
-      <c r="J47" s="20">
-        <v>0</v>
-      </c>
-      <c r="K47" s="20">
-        <v>0</v>
-      </c>
-      <c r="L47" s="20">
-        <v>0</v>
-      </c>
-      <c r="M47" s="20">
-        <v>0</v>
-      </c>
-      <c r="N47" s="20">
-        <v>0</v>
-      </c>
-      <c r="O47" s="18">
-        <f t="shared" ref="O47:O54" si="6">SUM(C47:N47)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B48" s="19" t="s">
+      <c r="C54" s="20">
+        <v>0</v>
+      </c>
+      <c r="D54" s="20">
+        <v>0</v>
+      </c>
+      <c r="E54" s="20">
+        <v>0</v>
+      </c>
+      <c r="F54" s="20">
+        <v>0</v>
+      </c>
+      <c r="G54" s="20">
+        <v>0</v>
+      </c>
+      <c r="H54" s="20">
+        <v>0</v>
+      </c>
+      <c r="I54" s="20">
+        <v>0</v>
+      </c>
+      <c r="J54" s="20">
+        <v>0</v>
+      </c>
+      <c r="K54" s="20">
+        <v>0</v>
+      </c>
+      <c r="L54" s="20">
+        <v>0</v>
+      </c>
+      <c r="M54" s="20">
+        <v>0</v>
+      </c>
+      <c r="N54" s="20">
+        <v>0</v>
+      </c>
+      <c r="O54" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="20">
-        <v>0</v>
-      </c>
-      <c r="D48" s="20">
-        <v>0</v>
-      </c>
-      <c r="E48" s="20">
-        <v>0</v>
-      </c>
-      <c r="F48" s="20">
-        <v>0</v>
-      </c>
-      <c r="G48" s="20">
-        <v>0</v>
-      </c>
-      <c r="H48" s="20">
-        <v>0</v>
-      </c>
-      <c r="I48" s="20">
-        <v>0</v>
-      </c>
-      <c r="J48" s="20">
-        <v>0</v>
-      </c>
-      <c r="K48" s="20">
-        <v>0</v>
-      </c>
-      <c r="L48" s="20">
-        <v>0</v>
-      </c>
-      <c r="M48" s="20">
-        <v>0</v>
-      </c>
-      <c r="N48" s="20">
-        <v>0</v>
-      </c>
-      <c r="O48" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B49" s="19" t="s">
+      <c r="C55" s="20">
+        <v>0</v>
+      </c>
+      <c r="D55" s="20">
+        <v>0</v>
+      </c>
+      <c r="E55" s="20">
+        <v>0</v>
+      </c>
+      <c r="F55" s="20">
+        <v>0</v>
+      </c>
+      <c r="G55" s="20">
+        <v>0</v>
+      </c>
+      <c r="H55" s="20">
+        <v>0</v>
+      </c>
+      <c r="I55" s="20">
+        <v>0</v>
+      </c>
+      <c r="J55" s="20">
+        <v>0</v>
+      </c>
+      <c r="K55" s="20">
+        <v>0</v>
+      </c>
+      <c r="L55" s="20">
+        <v>0</v>
+      </c>
+      <c r="M55" s="20">
+        <v>0</v>
+      </c>
+      <c r="N55" s="20">
+        <v>0</v>
+      </c>
+      <c r="O55" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="20">
-        <v>0</v>
-      </c>
-      <c r="D49" s="20">
-        <v>0</v>
-      </c>
-      <c r="E49" s="20">
-        <v>0</v>
-      </c>
-      <c r="F49" s="20">
-        <v>0</v>
-      </c>
-      <c r="G49" s="20">
-        <v>0</v>
-      </c>
-      <c r="H49" s="20">
-        <v>0</v>
-      </c>
-      <c r="I49" s="20">
-        <v>0</v>
-      </c>
-      <c r="J49" s="20">
-        <v>0</v>
-      </c>
-      <c r="K49" s="20">
-        <v>0</v>
-      </c>
-      <c r="L49" s="20">
-        <v>0</v>
-      </c>
-      <c r="M49" s="20">
-        <v>0</v>
-      </c>
-      <c r="N49" s="20">
-        <v>0</v>
-      </c>
-      <c r="O49" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B50" s="19" t="s">
+      <c r="C56" s="20">
+        <v>0</v>
+      </c>
+      <c r="D56" s="20">
+        <v>0</v>
+      </c>
+      <c r="E56" s="20">
+        <v>0</v>
+      </c>
+      <c r="F56" s="20">
+        <v>0</v>
+      </c>
+      <c r="G56" s="20">
+        <v>0</v>
+      </c>
+      <c r="H56" s="20">
+        <v>0</v>
+      </c>
+      <c r="I56" s="20">
+        <v>0</v>
+      </c>
+      <c r="J56" s="20">
+        <v>0</v>
+      </c>
+      <c r="K56" s="20">
+        <v>0</v>
+      </c>
+      <c r="L56" s="20">
+        <v>0</v>
+      </c>
+      <c r="M56" s="20">
+        <v>0</v>
+      </c>
+      <c r="N56" s="20">
+        <v>0</v>
+      </c>
+      <c r="O56" s="18">
+        <f t="shared" ref="O56" si="27">SUM(C56:N56)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="20">
-        <v>0</v>
-      </c>
-      <c r="D50" s="20">
-        <v>0</v>
-      </c>
-      <c r="E50" s="20">
-        <v>0</v>
-      </c>
-      <c r="F50" s="20">
-        <v>0</v>
-      </c>
-      <c r="G50" s="20">
-        <v>0</v>
-      </c>
-      <c r="H50" s="20">
-        <v>0</v>
-      </c>
-      <c r="I50" s="20">
-        <v>0</v>
-      </c>
-      <c r="J50" s="20">
-        <v>0</v>
-      </c>
-      <c r="K50" s="20">
-        <v>0</v>
-      </c>
-      <c r="L50" s="20">
-        <v>0</v>
-      </c>
-      <c r="M50" s="20">
-        <v>0</v>
-      </c>
-      <c r="N50" s="20">
-        <v>0</v>
-      </c>
-      <c r="O50" s="18">
-        <f t="shared" ref="O50" si="7">SUM(C50:N50)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B51" s="19" t="s">
+      <c r="C57" s="20">
+        <v>0</v>
+      </c>
+      <c r="D57" s="20">
+        <v>0</v>
+      </c>
+      <c r="E57" s="20">
+        <v>0</v>
+      </c>
+      <c r="F57" s="20">
+        <v>0</v>
+      </c>
+      <c r="G57" s="20">
+        <v>0</v>
+      </c>
+      <c r="H57" s="20">
+        <v>0</v>
+      </c>
+      <c r="I57" s="20">
+        <v>0</v>
+      </c>
+      <c r="J57" s="20">
+        <v>0</v>
+      </c>
+      <c r="K57" s="20">
+        <v>0</v>
+      </c>
+      <c r="L57" s="20">
+        <v>0</v>
+      </c>
+      <c r="M57" s="20">
+        <v>0</v>
+      </c>
+      <c r="N57" s="20">
+        <v>0</v>
+      </c>
+      <c r="O57" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="20">
-        <v>0</v>
-      </c>
-      <c r="D51" s="20">
-        <v>0</v>
-      </c>
-      <c r="E51" s="20">
-        <v>0</v>
-      </c>
-      <c r="F51" s="20">
-        <v>0</v>
-      </c>
-      <c r="G51" s="20">
-        <v>0</v>
-      </c>
-      <c r="H51" s="20">
-        <v>0</v>
-      </c>
-      <c r="I51" s="20">
-        <v>0</v>
-      </c>
-      <c r="J51" s="20">
-        <v>0</v>
-      </c>
-      <c r="K51" s="20">
-        <v>0</v>
-      </c>
-      <c r="L51" s="20">
-        <v>0</v>
-      </c>
-      <c r="M51" s="20">
-        <v>0</v>
-      </c>
-      <c r="N51" s="20">
-        <v>0</v>
-      </c>
-      <c r="O51" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B52" s="19" t="s">
+      <c r="C58" s="20">
+        <v>0</v>
+      </c>
+      <c r="D58" s="20">
+        <v>0</v>
+      </c>
+      <c r="E58" s="20">
+        <v>0</v>
+      </c>
+      <c r="F58" s="20">
+        <v>0</v>
+      </c>
+      <c r="G58" s="20">
+        <v>0</v>
+      </c>
+      <c r="H58" s="20">
+        <v>0</v>
+      </c>
+      <c r="I58" s="20">
+        <v>0</v>
+      </c>
+      <c r="J58" s="20">
+        <v>0</v>
+      </c>
+      <c r="K58" s="20">
+        <v>0</v>
+      </c>
+      <c r="L58" s="20">
+        <v>0</v>
+      </c>
+      <c r="M58" s="20">
+        <v>0</v>
+      </c>
+      <c r="N58" s="20">
+        <v>0</v>
+      </c>
+      <c r="O58" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="20">
-        <v>0</v>
-      </c>
-      <c r="D52" s="20">
-        <v>0</v>
-      </c>
-      <c r="E52" s="20">
-        <v>0</v>
-      </c>
-      <c r="F52" s="20">
-        <v>0</v>
-      </c>
-      <c r="G52" s="20">
-        <v>0</v>
-      </c>
-      <c r="H52" s="20">
-        <v>0</v>
-      </c>
-      <c r="I52" s="20">
-        <v>0</v>
-      </c>
-      <c r="J52" s="20">
-        <v>0</v>
-      </c>
-      <c r="K52" s="20">
-        <v>0</v>
-      </c>
-      <c r="L52" s="20">
-        <v>0</v>
-      </c>
-      <c r="M52" s="20">
-        <v>0</v>
-      </c>
-      <c r="N52" s="20">
-        <v>0</v>
-      </c>
-      <c r="O52" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B53" s="19" t="s">
+      <c r="C59" s="20">
+        <v>0</v>
+      </c>
+      <c r="D59" s="20">
+        <v>0</v>
+      </c>
+      <c r="E59" s="20">
+        <v>0</v>
+      </c>
+      <c r="F59" s="20">
+        <v>0</v>
+      </c>
+      <c r="G59" s="20">
+        <v>0</v>
+      </c>
+      <c r="H59" s="20">
+        <v>0</v>
+      </c>
+      <c r="I59" s="20">
+        <v>0</v>
+      </c>
+      <c r="J59" s="20">
+        <v>0</v>
+      </c>
+      <c r="K59" s="20">
+        <v>0</v>
+      </c>
+      <c r="L59" s="20">
+        <v>0</v>
+      </c>
+      <c r="M59" s="20">
+        <v>0</v>
+      </c>
+      <c r="N59" s="20">
+        <v>0</v>
+      </c>
+      <c r="O59" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="20">
-        <v>0</v>
-      </c>
-      <c r="D53" s="20">
-        <v>0</v>
-      </c>
-      <c r="E53" s="20">
-        <v>0</v>
-      </c>
-      <c r="F53" s="20">
-        <v>0</v>
-      </c>
-      <c r="G53" s="20">
-        <v>0</v>
-      </c>
-      <c r="H53" s="20">
-        <v>0</v>
-      </c>
-      <c r="I53" s="20">
-        <v>0</v>
-      </c>
-      <c r="J53" s="20">
-        <v>0</v>
-      </c>
-      <c r="K53" s="20">
-        <v>0</v>
-      </c>
-      <c r="L53" s="20">
-        <v>0</v>
-      </c>
-      <c r="M53" s="20">
-        <v>0</v>
-      </c>
-      <c r="N53" s="20">
-        <v>0</v>
-      </c>
-      <c r="O53" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B54" s="19" t="s">
+      <c r="C60" s="20">
+        <v>0</v>
+      </c>
+      <c r="D60" s="20">
+        <v>0</v>
+      </c>
+      <c r="E60" s="20">
+        <v>0</v>
+      </c>
+      <c r="F60" s="20">
+        <v>0</v>
+      </c>
+      <c r="G60" s="20">
+        <v>0</v>
+      </c>
+      <c r="H60" s="20">
+        <v>0</v>
+      </c>
+      <c r="I60" s="20">
+        <v>0</v>
+      </c>
+      <c r="J60" s="20">
+        <v>0</v>
+      </c>
+      <c r="K60" s="20">
+        <v>0</v>
+      </c>
+      <c r="L60" s="20">
+        <v>0</v>
+      </c>
+      <c r="M60" s="20">
+        <v>0</v>
+      </c>
+      <c r="N60" s="20">
+        <v>0</v>
+      </c>
+      <c r="O60" s="18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="45"/>
+      <c r="C61" s="20">
+        <v>0</v>
+      </c>
+      <c r="D61" s="20">
+        <v>0</v>
+      </c>
+      <c r="E61" s="20">
+        <v>0</v>
+      </c>
+      <c r="F61" s="20">
+        <v>0</v>
+      </c>
+      <c r="G61" s="20">
+        <v>0</v>
+      </c>
+      <c r="H61" s="20">
+        <v>0</v>
+      </c>
+      <c r="I61" s="20">
+        <v>0</v>
+      </c>
+      <c r="J61" s="20">
+        <v>0</v>
+      </c>
+      <c r="K61" s="20">
+        <v>0</v>
+      </c>
+      <c r="L61" s="20">
+        <v>0</v>
+      </c>
+      <c r="M61" s="20">
+        <v>0</v>
+      </c>
+      <c r="N61" s="20">
+        <v>0</v>
+      </c>
+      <c r="O61" s="18">
+        <f t="shared" ref="O61" si="28">SUM(C61:N61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C62" s="44">
+        <f>SUM(C51:C61)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="44">
+        <f t="shared" ref="D62:O62" si="29">SUM(D51:D61)</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="M62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="N62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="O62" s="44">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="C54" s="20">
-        <v>0</v>
-      </c>
-      <c r="D54" s="20">
-        <v>0</v>
-      </c>
-      <c r="E54" s="20">
-        <v>0</v>
-      </c>
-      <c r="F54" s="20">
-        <v>0</v>
-      </c>
-      <c r="G54" s="20">
-        <v>0</v>
-      </c>
-      <c r="H54" s="20">
-        <v>0</v>
-      </c>
-      <c r="I54" s="20">
-        <v>0</v>
-      </c>
-      <c r="J54" s="20">
-        <v>0</v>
-      </c>
-      <c r="K54" s="20">
-        <v>0</v>
-      </c>
-      <c r="L54" s="20">
-        <v>0</v>
-      </c>
-      <c r="M54" s="20">
-        <v>0</v>
-      </c>
-      <c r="N54" s="20">
-        <v>0</v>
-      </c>
-      <c r="O54" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B55" s="19"/>
-      <c r="C55" s="44"/>
-      <c r="D55" s="44"/>
-      <c r="E55" s="44"/>
-      <c r="F55" s="44"/>
-      <c r="G55" s="44"/>
-      <c r="H55" s="44"/>
-      <c r="I55" s="44"/>
-      <c r="J55" s="44"/>
-      <c r="K55" s="44"/>
-      <c r="L55" s="44"/>
-      <c r="M55" s="44"/>
-      <c r="N55" s="44"/>
-      <c r="O55" s="34"/>
-    </row>
-    <row r="56" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B56" s="16" t="s">
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
+      <c r="K63" s="22"/>
+      <c r="L63" s="22"/>
+      <c r="M63" s="22"/>
+      <c r="N63" s="29"/>
+      <c r="O63" s="21"/>
+    </row>
+    <row r="64" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="22"/>
-      <c r="J56" s="22"/>
-      <c r="K56" s="22"/>
-      <c r="L56" s="22"/>
-      <c r="M56" s="22"/>
-      <c r="N56" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O56" s="21">
-        <f>SUM(O57:O60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B57" s="19" t="s">
+      <c r="C64" s="20">
+        <v>0</v>
+      </c>
+      <c r="D64" s="20">
+        <v>0</v>
+      </c>
+      <c r="E64" s="20">
+        <v>0</v>
+      </c>
+      <c r="F64" s="20">
+        <v>0</v>
+      </c>
+      <c r="G64" s="20">
+        <v>0</v>
+      </c>
+      <c r="H64" s="20">
+        <v>0</v>
+      </c>
+      <c r="I64" s="20">
+        <v>0</v>
+      </c>
+      <c r="J64" s="20">
+        <v>0</v>
+      </c>
+      <c r="K64" s="20">
+        <v>0</v>
+      </c>
+      <c r="L64" s="20">
+        <v>0</v>
+      </c>
+      <c r="M64" s="20">
+        <v>0</v>
+      </c>
+      <c r="N64" s="20">
+        <v>0</v>
+      </c>
+      <c r="O64" s="18">
+        <f t="shared" ref="O64:O73" si="30">SUM(C64:N64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C57" s="20">
-        <v>0</v>
-      </c>
-      <c r="D57" s="20">
-        <v>0</v>
-      </c>
-      <c r="E57" s="20">
-        <v>0</v>
-      </c>
-      <c r="F57" s="20">
-        <v>0</v>
-      </c>
-      <c r="G57" s="20">
-        <v>0</v>
-      </c>
-      <c r="H57" s="20">
-        <v>0</v>
-      </c>
-      <c r="I57" s="20">
-        <v>0</v>
-      </c>
-      <c r="J57" s="20">
-        <v>0</v>
-      </c>
-      <c r="K57" s="20">
-        <v>0</v>
-      </c>
-      <c r="L57" s="20">
-        <v>0</v>
-      </c>
-      <c r="M57" s="20">
-        <v>0</v>
-      </c>
-      <c r="N57" s="20">
-        <v>0</v>
-      </c>
-      <c r="O57" s="18">
-        <f t="shared" ref="O57:O65" si="8">SUM(C57:N57)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B58" s="19" t="s">
+      <c r="C65" s="20">
+        <v>0</v>
+      </c>
+      <c r="D65" s="20">
+        <v>0</v>
+      </c>
+      <c r="E65" s="20">
+        <v>0</v>
+      </c>
+      <c r="F65" s="20">
+        <v>0</v>
+      </c>
+      <c r="G65" s="20">
+        <v>0</v>
+      </c>
+      <c r="H65" s="20">
+        <v>0</v>
+      </c>
+      <c r="I65" s="20">
+        <v>0</v>
+      </c>
+      <c r="J65" s="20">
+        <v>0</v>
+      </c>
+      <c r="K65" s="20">
+        <v>0</v>
+      </c>
+      <c r="L65" s="20">
+        <v>0</v>
+      </c>
+      <c r="M65" s="20">
+        <v>0</v>
+      </c>
+      <c r="N65" s="20">
+        <v>0</v>
+      </c>
+      <c r="O65" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C58" s="20">
-        <v>0</v>
-      </c>
-      <c r="D58" s="20">
-        <v>0</v>
-      </c>
-      <c r="E58" s="20">
-        <v>0</v>
-      </c>
-      <c r="F58" s="20">
-        <v>0</v>
-      </c>
-      <c r="G58" s="20">
-        <v>0</v>
-      </c>
-      <c r="H58" s="20">
-        <v>0</v>
-      </c>
-      <c r="I58" s="20">
-        <v>0</v>
-      </c>
-      <c r="J58" s="20">
-        <v>0</v>
-      </c>
-      <c r="K58" s="20">
-        <v>0</v>
-      </c>
-      <c r="L58" s="20">
-        <v>0</v>
-      </c>
-      <c r="M58" s="20">
-        <v>0</v>
-      </c>
-      <c r="N58" s="20">
-        <v>0</v>
-      </c>
-      <c r="O58" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B59" s="19" t="s">
+      <c r="C66" s="20">
+        <v>0</v>
+      </c>
+      <c r="D66" s="20">
+        <v>0</v>
+      </c>
+      <c r="E66" s="20">
+        <v>0</v>
+      </c>
+      <c r="F66" s="20">
+        <v>0</v>
+      </c>
+      <c r="G66" s="20">
+        <v>0</v>
+      </c>
+      <c r="H66" s="20">
+        <v>0</v>
+      </c>
+      <c r="I66" s="20">
+        <v>0</v>
+      </c>
+      <c r="J66" s="20">
+        <v>0</v>
+      </c>
+      <c r="K66" s="20">
+        <v>0</v>
+      </c>
+      <c r="L66" s="20">
+        <v>0</v>
+      </c>
+      <c r="M66" s="20">
+        <v>0</v>
+      </c>
+      <c r="N66" s="20">
+        <v>0</v>
+      </c>
+      <c r="O66" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="45"/>
+      <c r="C67" s="20">
+        <v>0</v>
+      </c>
+      <c r="D67" s="20">
+        <v>0</v>
+      </c>
+      <c r="E67" s="20">
+        <v>0</v>
+      </c>
+      <c r="F67" s="20">
+        <v>0</v>
+      </c>
+      <c r="G67" s="20">
+        <v>0</v>
+      </c>
+      <c r="H67" s="20">
+        <v>0</v>
+      </c>
+      <c r="I67" s="20">
+        <v>0</v>
+      </c>
+      <c r="J67" s="20">
+        <v>0</v>
+      </c>
+      <c r="K67" s="20">
+        <v>0</v>
+      </c>
+      <c r="L67" s="20">
+        <v>0</v>
+      </c>
+      <c r="M67" s="20">
+        <v>0</v>
+      </c>
+      <c r="N67" s="20">
+        <v>0</v>
+      </c>
+      <c r="O67" s="18">
+        <f t="shared" ref="O67" si="31">SUM(C67:N67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C68" s="44">
+        <f>SUM(C64:C67)</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="44">
+        <f t="shared" ref="D68:O68" si="32">SUM(D64:D67)</f>
+        <v>0</v>
+      </c>
+      <c r="E68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="G68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="I68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="J68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="N68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O68" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C59" s="20">
-        <v>0</v>
-      </c>
-      <c r="D59" s="20">
-        <v>0</v>
-      </c>
-      <c r="E59" s="20">
-        <v>0</v>
-      </c>
-      <c r="F59" s="20">
-        <v>0</v>
-      </c>
-      <c r="G59" s="20">
-        <v>0</v>
-      </c>
-      <c r="H59" s="20">
-        <v>0</v>
-      </c>
-      <c r="I59" s="20">
-        <v>0</v>
-      </c>
-      <c r="J59" s="20">
-        <v>0</v>
-      </c>
-      <c r="K59" s="20">
-        <v>0</v>
-      </c>
-      <c r="L59" s="20">
-        <v>0</v>
-      </c>
-      <c r="M59" s="20">
-        <v>0</v>
-      </c>
-      <c r="N59" s="20">
-        <v>0</v>
-      </c>
-      <c r="O59" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B60" s="19"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="20"/>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
-      <c r="N60" s="20"/>
-      <c r="O60" s="18"/>
-    </row>
-    <row r="61" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B61" s="16" t="s">
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="29"/>
+      <c r="O69" s="21"/>
+    </row>
+    <row r="70" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O61" s="21">
-        <f>SUM(O62:O66)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B62" s="19" t="s">
+      <c r="C70" s="20">
+        <v>0</v>
+      </c>
+      <c r="D70" s="20">
+        <v>0</v>
+      </c>
+      <c r="E70" s="20">
+        <v>0</v>
+      </c>
+      <c r="F70" s="20">
+        <v>0</v>
+      </c>
+      <c r="G70" s="20">
+        <v>0</v>
+      </c>
+      <c r="H70" s="20">
+        <v>0</v>
+      </c>
+      <c r="I70" s="20">
+        <v>0</v>
+      </c>
+      <c r="J70" s="20">
+        <v>0</v>
+      </c>
+      <c r="K70" s="20">
+        <v>0</v>
+      </c>
+      <c r="L70" s="20">
+        <v>0</v>
+      </c>
+      <c r="M70" s="20">
+        <v>0</v>
+      </c>
+      <c r="N70" s="20">
+        <v>0</v>
+      </c>
+      <c r="O70" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C62" s="20">
-        <v>0</v>
-      </c>
-      <c r="D62" s="20">
-        <v>0</v>
-      </c>
-      <c r="E62" s="20">
-        <v>0</v>
-      </c>
-      <c r="F62" s="20">
-        <v>0</v>
-      </c>
-      <c r="G62" s="20">
-        <v>0</v>
-      </c>
-      <c r="H62" s="20">
-        <v>0</v>
-      </c>
-      <c r="I62" s="20">
-        <v>0</v>
-      </c>
-      <c r="J62" s="20">
-        <v>0</v>
-      </c>
-      <c r="K62" s="20">
-        <v>0</v>
-      </c>
-      <c r="L62" s="20">
-        <v>0</v>
-      </c>
-      <c r="M62" s="20">
-        <v>0</v>
-      </c>
-      <c r="N62" s="20">
-        <v>0</v>
-      </c>
-      <c r="O62" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B63" s="19" t="s">
+      <c r="C71" s="20">
+        <v>0</v>
+      </c>
+      <c r="D71" s="20">
+        <v>0</v>
+      </c>
+      <c r="E71" s="20">
+        <v>0</v>
+      </c>
+      <c r="F71" s="20">
+        <v>0</v>
+      </c>
+      <c r="G71" s="20">
+        <v>0</v>
+      </c>
+      <c r="H71" s="20">
+        <v>0</v>
+      </c>
+      <c r="I71" s="20">
+        <v>0</v>
+      </c>
+      <c r="J71" s="20">
+        <v>0</v>
+      </c>
+      <c r="K71" s="20">
+        <v>0</v>
+      </c>
+      <c r="L71" s="20">
+        <v>0</v>
+      </c>
+      <c r="M71" s="20">
+        <v>0</v>
+      </c>
+      <c r="N71" s="20">
+        <v>0</v>
+      </c>
+      <c r="O71" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C63" s="20">
-        <v>0</v>
-      </c>
-      <c r="D63" s="20">
-        <v>0</v>
-      </c>
-      <c r="E63" s="20">
-        <v>0</v>
-      </c>
-      <c r="F63" s="20">
-        <v>0</v>
-      </c>
-      <c r="G63" s="20">
-        <v>0</v>
-      </c>
-      <c r="H63" s="20">
-        <v>0</v>
-      </c>
-      <c r="I63" s="20">
-        <v>0</v>
-      </c>
-      <c r="J63" s="20">
-        <v>0</v>
-      </c>
-      <c r="K63" s="20">
-        <v>0</v>
-      </c>
-      <c r="L63" s="20">
-        <v>0</v>
-      </c>
-      <c r="M63" s="20">
-        <v>0</v>
-      </c>
-      <c r="N63" s="20">
-        <v>0</v>
-      </c>
-      <c r="O63" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B64" s="19" t="s">
+      <c r="C72" s="20">
+        <v>0</v>
+      </c>
+      <c r="D72" s="20">
+        <v>0</v>
+      </c>
+      <c r="E72" s="20">
+        <v>0</v>
+      </c>
+      <c r="F72" s="20">
+        <v>0</v>
+      </c>
+      <c r="G72" s="20">
+        <v>0</v>
+      </c>
+      <c r="H72" s="20">
+        <v>0</v>
+      </c>
+      <c r="I72" s="20">
+        <v>0</v>
+      </c>
+      <c r="J72" s="20">
+        <v>0</v>
+      </c>
+      <c r="K72" s="20">
+        <v>0</v>
+      </c>
+      <c r="L72" s="20">
+        <v>0</v>
+      </c>
+      <c r="M72" s="20">
+        <v>0</v>
+      </c>
+      <c r="N72" s="20">
+        <v>0</v>
+      </c>
+      <c r="O72" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C64" s="20">
-        <v>0</v>
-      </c>
-      <c r="D64" s="20">
-        <v>0</v>
-      </c>
-      <c r="E64" s="20">
-        <v>0</v>
-      </c>
-      <c r="F64" s="20">
-        <v>0</v>
-      </c>
-      <c r="G64" s="20">
-        <v>0</v>
-      </c>
-      <c r="H64" s="20">
-        <v>0</v>
-      </c>
-      <c r="I64" s="20">
-        <v>0</v>
-      </c>
-      <c r="J64" s="20">
-        <v>0</v>
-      </c>
-      <c r="K64" s="20">
-        <v>0</v>
-      </c>
-      <c r="L64" s="20">
-        <v>0</v>
-      </c>
-      <c r="M64" s="20">
-        <v>0</v>
-      </c>
-      <c r="N64" s="20">
-        <v>0</v>
-      </c>
-      <c r="O64" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B65" s="19" t="s">
+      <c r="C73" s="20">
+        <v>0</v>
+      </c>
+      <c r="D73" s="20">
+        <v>0</v>
+      </c>
+      <c r="E73" s="20">
+        <v>0</v>
+      </c>
+      <c r="F73" s="20">
+        <v>0</v>
+      </c>
+      <c r="G73" s="20">
+        <v>0</v>
+      </c>
+      <c r="H73" s="20">
+        <v>0</v>
+      </c>
+      <c r="I73" s="20">
+        <v>0</v>
+      </c>
+      <c r="J73" s="20">
+        <v>0</v>
+      </c>
+      <c r="K73" s="20">
+        <v>0</v>
+      </c>
+      <c r="L73" s="20">
+        <v>0</v>
+      </c>
+      <c r="M73" s="20">
+        <v>0</v>
+      </c>
+      <c r="N73" s="20">
+        <v>0</v>
+      </c>
+      <c r="O73" s="18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="45"/>
+      <c r="C74" s="20">
+        <v>0</v>
+      </c>
+      <c r="D74" s="20">
+        <v>0</v>
+      </c>
+      <c r="E74" s="20">
+        <v>0</v>
+      </c>
+      <c r="F74" s="20">
+        <v>0</v>
+      </c>
+      <c r="G74" s="20">
+        <v>0</v>
+      </c>
+      <c r="H74" s="20">
+        <v>0</v>
+      </c>
+      <c r="I74" s="20">
+        <v>0</v>
+      </c>
+      <c r="J74" s="20">
+        <v>0</v>
+      </c>
+      <c r="K74" s="20">
+        <v>0</v>
+      </c>
+      <c r="L74" s="20">
+        <v>0</v>
+      </c>
+      <c r="M74" s="20">
+        <v>0</v>
+      </c>
+      <c r="N74" s="20">
+        <v>0</v>
+      </c>
+      <c r="O74" s="18">
+        <f t="shared" ref="O74" si="33">SUM(C74:N74)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C75" s="44">
+        <f>SUM(C70:C74)</f>
+        <v>0</v>
+      </c>
+      <c r="D75" s="44">
+        <f t="shared" ref="D75:O75" si="34">SUM(D70:D74)</f>
+        <v>0</v>
+      </c>
+      <c r="E75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="G75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="I75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="J75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="K75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="L75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="N75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="O75" s="44">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" s="36" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="20">
-        <v>0</v>
-      </c>
-      <c r="D65" s="20">
-        <v>0</v>
-      </c>
-      <c r="E65" s="20">
-        <v>0</v>
-      </c>
-      <c r="F65" s="20">
-        <v>0</v>
-      </c>
-      <c r="G65" s="20">
-        <v>0</v>
-      </c>
-      <c r="H65" s="20">
-        <v>0</v>
-      </c>
-      <c r="I65" s="20">
-        <v>0</v>
-      </c>
-      <c r="J65" s="20">
-        <v>0</v>
-      </c>
-      <c r="K65" s="20">
-        <v>0</v>
-      </c>
-      <c r="L65" s="20">
-        <v>0</v>
-      </c>
-      <c r="M65" s="20">
-        <v>0</v>
-      </c>
-      <c r="N65" s="20">
-        <v>0</v>
-      </c>
-      <c r="O65" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B66" s="19"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
-      <c r="H66" s="20"/>
-      <c r="I66" s="20"/>
-      <c r="J66" s="20"/>
-      <c r="K66" s="20"/>
-      <c r="L66" s="20"/>
-      <c r="M66" s="20"/>
-      <c r="N66" s="20"/>
-      <c r="O66" s="18"/>
-    </row>
-    <row r="67" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B67" s="16" t="s">
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="23"/>
+      <c r="J76" s="23"/>
+      <c r="K76" s="23"/>
+      <c r="L76" s="23"/>
+      <c r="M76" s="23"/>
+      <c r="N76" s="29"/>
+      <c r="O76" s="21"/>
+    </row>
+    <row r="77" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C67" s="23"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="23"/>
-      <c r="H67" s="23"/>
-      <c r="I67" s="23"/>
-      <c r="J67" s="23"/>
-      <c r="K67" s="23"/>
-      <c r="L67" s="23"/>
-      <c r="M67" s="23"/>
-      <c r="N67" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O67" s="21">
-        <f>SUM(O68:O91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B68" s="19" t="s">
+      <c r="C77" s="20">
+        <v>0</v>
+      </c>
+      <c r="D77" s="20">
+        <v>0</v>
+      </c>
+      <c r="E77" s="20">
+        <v>0</v>
+      </c>
+      <c r="F77" s="20">
+        <v>0</v>
+      </c>
+      <c r="G77" s="20">
+        <v>0</v>
+      </c>
+      <c r="H77" s="20">
+        <v>0</v>
+      </c>
+      <c r="I77" s="20">
+        <v>0</v>
+      </c>
+      <c r="J77" s="20">
+        <v>0</v>
+      </c>
+      <c r="K77" s="20">
+        <v>0</v>
+      </c>
+      <c r="L77" s="20">
+        <v>0</v>
+      </c>
+      <c r="M77" s="20">
+        <v>0</v>
+      </c>
+      <c r="N77" s="20">
+        <v>0</v>
+      </c>
+      <c r="O77" s="18">
+        <f t="shared" ref="O77:O102" si="35">SUM(C77:N77)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C68" s="20">
-        <v>0</v>
-      </c>
-      <c r="D68" s="20">
-        <v>0</v>
-      </c>
-      <c r="E68" s="20">
-        <v>0</v>
-      </c>
-      <c r="F68" s="20">
-        <v>0</v>
-      </c>
-      <c r="G68" s="20">
-        <v>0</v>
-      </c>
-      <c r="H68" s="20">
-        <v>0</v>
-      </c>
-      <c r="I68" s="20">
-        <v>0</v>
-      </c>
-      <c r="J68" s="20">
-        <v>0</v>
-      </c>
-      <c r="K68" s="20">
-        <v>0</v>
-      </c>
-      <c r="L68" s="20">
-        <v>0</v>
-      </c>
-      <c r="M68" s="20">
-        <v>0</v>
-      </c>
-      <c r="N68" s="20">
-        <v>0</v>
-      </c>
-      <c r="O68" s="18">
-        <f t="shared" ref="O68:O90" si="9">SUM(C68:N68)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B69" s="19" t="s">
+      <c r="C78" s="20">
+        <v>0</v>
+      </c>
+      <c r="D78" s="20">
+        <v>0</v>
+      </c>
+      <c r="E78" s="20">
+        <v>0</v>
+      </c>
+      <c r="F78" s="20">
+        <v>0</v>
+      </c>
+      <c r="G78" s="20">
+        <v>0</v>
+      </c>
+      <c r="H78" s="20">
+        <v>0</v>
+      </c>
+      <c r="I78" s="20">
+        <v>0</v>
+      </c>
+      <c r="J78" s="20">
+        <v>0</v>
+      </c>
+      <c r="K78" s="20">
+        <v>0</v>
+      </c>
+      <c r="L78" s="20">
+        <v>0</v>
+      </c>
+      <c r="M78" s="20">
+        <v>0</v>
+      </c>
+      <c r="N78" s="20">
+        <v>0</v>
+      </c>
+      <c r="O78" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C69" s="20">
-        <v>0</v>
-      </c>
-      <c r="D69" s="20">
-        <v>0</v>
-      </c>
-      <c r="E69" s="20">
-        <v>0</v>
-      </c>
-      <c r="F69" s="20">
-        <v>0</v>
-      </c>
-      <c r="G69" s="20">
-        <v>0</v>
-      </c>
-      <c r="H69" s="20">
-        <v>0</v>
-      </c>
-      <c r="I69" s="20">
-        <v>0</v>
-      </c>
-      <c r="J69" s="20">
-        <v>0</v>
-      </c>
-      <c r="K69" s="20">
-        <v>0</v>
-      </c>
-      <c r="L69" s="20">
-        <v>0</v>
-      </c>
-      <c r="M69" s="20">
-        <v>0</v>
-      </c>
-      <c r="N69" s="20">
-        <v>0</v>
-      </c>
-      <c r="O69" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B70" s="19" t="s">
+      <c r="C79" s="20">
+        <v>0</v>
+      </c>
+      <c r="D79" s="20">
+        <v>0</v>
+      </c>
+      <c r="E79" s="20">
+        <v>0</v>
+      </c>
+      <c r="F79" s="20">
+        <v>0</v>
+      </c>
+      <c r="G79" s="20">
+        <v>0</v>
+      </c>
+      <c r="H79" s="20">
+        <v>0</v>
+      </c>
+      <c r="I79" s="20">
+        <v>0</v>
+      </c>
+      <c r="J79" s="20">
+        <v>0</v>
+      </c>
+      <c r="K79" s="20">
+        <v>0</v>
+      </c>
+      <c r="L79" s="20">
+        <v>0</v>
+      </c>
+      <c r="M79" s="20">
+        <v>0</v>
+      </c>
+      <c r="N79" s="20">
+        <v>0</v>
+      </c>
+      <c r="O79" s="18">
+        <f t="shared" ref="O79:O80" si="36">SUM(C79:N79)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:15" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="C70" s="20">
-        <v>0</v>
-      </c>
-      <c r="D70" s="20">
-        <v>0</v>
-      </c>
-      <c r="E70" s="20">
-        <v>0</v>
-      </c>
-      <c r="F70" s="20">
-        <v>0</v>
-      </c>
-      <c r="G70" s="20">
-        <v>0</v>
-      </c>
-      <c r="H70" s="20">
-        <v>0</v>
-      </c>
-      <c r="I70" s="20">
-        <v>0</v>
-      </c>
-      <c r="J70" s="20">
-        <v>0</v>
-      </c>
-      <c r="K70" s="20">
-        <v>0</v>
-      </c>
-      <c r="L70" s="20">
-        <v>0</v>
-      </c>
-      <c r="M70" s="20">
-        <v>0</v>
-      </c>
-      <c r="N70" s="20">
-        <v>0</v>
-      </c>
-      <c r="O70" s="18">
-        <f t="shared" ref="O70:O71" si="10">SUM(C70:N70)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B71" s="19" t="s">
+      <c r="C80" s="20">
+        <v>0</v>
+      </c>
+      <c r="D80" s="20">
+        <v>0</v>
+      </c>
+      <c r="E80" s="20">
+        <v>0</v>
+      </c>
+      <c r="F80" s="20">
+        <v>0</v>
+      </c>
+      <c r="G80" s="20">
+        <v>0</v>
+      </c>
+      <c r="H80" s="20">
+        <v>0</v>
+      </c>
+      <c r="I80" s="20">
+        <v>0</v>
+      </c>
+      <c r="J80" s="20">
+        <v>0</v>
+      </c>
+      <c r="K80" s="20">
+        <v>0</v>
+      </c>
+      <c r="L80" s="20">
+        <v>0</v>
+      </c>
+      <c r="M80" s="20">
+        <v>0</v>
+      </c>
+      <c r="N80" s="20">
+        <v>0</v>
+      </c>
+      <c r="O80" s="18">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C71" s="20">
-        <v>0</v>
-      </c>
-      <c r="D71" s="20">
-        <v>0</v>
-      </c>
-      <c r="E71" s="20">
-        <v>0</v>
-      </c>
-      <c r="F71" s="20">
-        <v>0</v>
-      </c>
-      <c r="G71" s="20">
-        <v>0</v>
-      </c>
-      <c r="H71" s="20">
-        <v>0</v>
-      </c>
-      <c r="I71" s="20">
-        <v>0</v>
-      </c>
-      <c r="J71" s="20">
-        <v>0</v>
-      </c>
-      <c r="K71" s="20">
-        <v>0</v>
-      </c>
-      <c r="L71" s="20">
-        <v>0</v>
-      </c>
-      <c r="M71" s="20">
-        <v>0</v>
-      </c>
-      <c r="N71" s="20">
-        <v>0</v>
-      </c>
-      <c r="O71" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B72" s="19" t="s">
+      <c r="C81" s="20">
+        <v>0</v>
+      </c>
+      <c r="D81" s="20">
+        <v>0</v>
+      </c>
+      <c r="E81" s="20">
+        <v>0</v>
+      </c>
+      <c r="F81" s="20">
+        <v>0</v>
+      </c>
+      <c r="G81" s="20">
+        <v>0</v>
+      </c>
+      <c r="H81" s="20">
+        <v>0</v>
+      </c>
+      <c r="I81" s="20">
+        <v>0</v>
+      </c>
+      <c r="J81" s="20">
+        <v>0</v>
+      </c>
+      <c r="K81" s="20">
+        <v>0</v>
+      </c>
+      <c r="L81" s="20">
+        <v>0</v>
+      </c>
+      <c r="M81" s="20">
+        <v>0</v>
+      </c>
+      <c r="N81" s="20">
+        <v>0</v>
+      </c>
+      <c r="O81" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C72" s="20">
-        <v>0</v>
-      </c>
-      <c r="D72" s="20">
-        <v>0</v>
-      </c>
-      <c r="E72" s="20">
-        <v>0</v>
-      </c>
-      <c r="F72" s="20">
-        <v>0</v>
-      </c>
-      <c r="G72" s="20">
-        <v>0</v>
-      </c>
-      <c r="H72" s="20">
-        <v>0</v>
-      </c>
-      <c r="I72" s="20">
-        <v>0</v>
-      </c>
-      <c r="J72" s="20">
-        <v>0</v>
-      </c>
-      <c r="K72" s="20">
-        <v>0</v>
-      </c>
-      <c r="L72" s="20">
-        <v>0</v>
-      </c>
-      <c r="M72" s="20">
-        <v>0</v>
-      </c>
-      <c r="N72" s="20">
-        <v>0</v>
-      </c>
-      <c r="O72" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B73" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C73" s="20">
-        <v>0</v>
-      </c>
-      <c r="D73" s="20">
-        <v>0</v>
-      </c>
-      <c r="E73" s="20">
-        <v>0</v>
-      </c>
-      <c r="F73" s="20">
-        <v>0</v>
-      </c>
-      <c r="G73" s="20">
-        <v>0</v>
-      </c>
-      <c r="H73" s="20">
-        <v>0</v>
-      </c>
-      <c r="I73" s="20">
-        <v>0</v>
-      </c>
-      <c r="J73" s="20">
-        <v>0</v>
-      </c>
-      <c r="K73" s="20">
-        <v>0</v>
-      </c>
-      <c r="L73" s="20">
-        <v>0</v>
-      </c>
-      <c r="M73" s="20">
-        <v>0</v>
-      </c>
-      <c r="N73" s="20">
-        <v>0</v>
-      </c>
-      <c r="O73" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B74" s="19"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="20"/>
-      <c r="K74" s="20"/>
-      <c r="L74" s="20"/>
-      <c r="M74" s="20"/>
-      <c r="N74" s="20"/>
-      <c r="O74" s="18"/>
-    </row>
-    <row r="75" spans="2:15" s="38" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B75" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
-      <c r="J75" s="37"/>
-      <c r="K75" s="37"/>
-      <c r="L75" s="37"/>
-      <c r="M75" s="37"/>
-      <c r="N75" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O75" s="21">
-        <f>SUM(O76:O79)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B76" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" s="20">
-        <v>0</v>
-      </c>
-      <c r="D76" s="20">
-        <v>0</v>
-      </c>
-      <c r="E76" s="20">
-        <v>0</v>
-      </c>
-      <c r="F76" s="20">
-        <v>0</v>
-      </c>
-      <c r="G76" s="20">
-        <v>0</v>
-      </c>
-      <c r="H76" s="20">
-        <v>0</v>
-      </c>
-      <c r="I76" s="20">
-        <v>0</v>
-      </c>
-      <c r="J76" s="20">
-        <v>0</v>
-      </c>
-      <c r="K76" s="20">
-        <v>0</v>
-      </c>
-      <c r="L76" s="20">
-        <v>0</v>
-      </c>
-      <c r="M76" s="20">
-        <v>0</v>
-      </c>
-      <c r="N76" s="20">
-        <v>0</v>
-      </c>
-      <c r="O76" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B77" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" s="20">
-        <v>0</v>
-      </c>
-      <c r="D77" s="20">
-        <v>0</v>
-      </c>
-      <c r="E77" s="20">
-        <v>0</v>
-      </c>
-      <c r="F77" s="20">
-        <v>0</v>
-      </c>
-      <c r="G77" s="20">
-        <v>0</v>
-      </c>
-      <c r="H77" s="20">
-        <v>0</v>
-      </c>
-      <c r="I77" s="20">
-        <v>0</v>
-      </c>
-      <c r="J77" s="20">
-        <v>0</v>
-      </c>
-      <c r="K77" s="20">
-        <v>0</v>
-      </c>
-      <c r="L77" s="20">
-        <v>0</v>
-      </c>
-      <c r="M77" s="20">
-        <v>0</v>
-      </c>
-      <c r="N77" s="20">
-        <v>0</v>
-      </c>
-      <c r="O77" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B78" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" s="20">
-        <v>0</v>
-      </c>
-      <c r="D78" s="20">
-        <v>0</v>
-      </c>
-      <c r="E78" s="20">
-        <v>0</v>
-      </c>
-      <c r="F78" s="20">
-        <v>0</v>
-      </c>
-      <c r="G78" s="20">
-        <v>0</v>
-      </c>
-      <c r="H78" s="20">
-        <v>0</v>
-      </c>
-      <c r="I78" s="20">
-        <v>0</v>
-      </c>
-      <c r="J78" s="20">
-        <v>0</v>
-      </c>
-      <c r="K78" s="20">
-        <v>0</v>
-      </c>
-      <c r="L78" s="20">
-        <v>0</v>
-      </c>
-      <c r="M78" s="20">
-        <v>0</v>
-      </c>
-      <c r="N78" s="20">
-        <v>0</v>
-      </c>
-      <c r="O78" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:15" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B79" s="19"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
-      <c r="J79" s="20"/>
-      <c r="K79" s="20"/>
-      <c r="L79" s="20"/>
-      <c r="M79" s="20"/>
-      <c r="N79" s="20"/>
-      <c r="O79" s="18"/>
-    </row>
-    <row r="80" spans="2:15" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B80" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
-      <c r="J80" s="36"/>
-      <c r="K80" s="36"/>
-      <c r="L80" s="36"/>
-      <c r="M80" s="36"/>
-      <c r="N80" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O80" s="21">
-        <f>SUM(O81:O84)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:117" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B81" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C81" s="20">
-        <v>0</v>
-      </c>
-      <c r="D81" s="20">
-        <v>0</v>
-      </c>
-      <c r="E81" s="20">
-        <v>0</v>
-      </c>
-      <c r="F81" s="20">
-        <v>0</v>
-      </c>
-      <c r="G81" s="20">
-        <v>0</v>
-      </c>
-      <c r="H81" s="20">
-        <v>0</v>
-      </c>
-      <c r="I81" s="20">
-        <v>0</v>
-      </c>
-      <c r="J81" s="20">
-        <v>0</v>
-      </c>
-      <c r="K81" s="20">
-        <v>0</v>
-      </c>
-      <c r="L81" s="20">
-        <v>0</v>
-      </c>
-      <c r="M81" s="20">
-        <v>0</v>
-      </c>
-      <c r="N81" s="20">
-        <v>0</v>
-      </c>
-      <c r="O81" s="18">
-        <f t="shared" ref="O81" si="11">SUM(C81:N81)</f>
-        <v>0</v>
-      </c>
-      <c r="P81" s="15"/>
-      <c r="Q81" s="15"/>
-      <c r="R81" s="15"/>
-      <c r="S81" s="15"/>
-      <c r="T81" s="15"/>
-      <c r="U81" s="15"/>
-      <c r="V81" s="15"/>
-      <c r="W81" s="15"/>
-      <c r="X81" s="15"/>
-      <c r="Y81" s="15"/>
-      <c r="Z81" s="15"/>
-      <c r="AA81" s="15"/>
-      <c r="AB81" s="15"/>
-      <c r="AC81" s="15"/>
-      <c r="AD81" s="15"/>
-      <c r="AE81" s="15"/>
-      <c r="AF81" s="15"/>
-      <c r="AG81" s="15"/>
-      <c r="AH81" s="15"/>
-      <c r="AI81" s="15"/>
-      <c r="AJ81" s="15"/>
-      <c r="AK81" s="15"/>
-      <c r="AL81" s="15"/>
-      <c r="AM81" s="15"/>
-      <c r="AN81" s="15"/>
-      <c r="AO81" s="15"/>
-      <c r="AP81" s="15"/>
-      <c r="AQ81" s="15"/>
-      <c r="AR81" s="15"/>
-      <c r="AS81" s="15"/>
-      <c r="AT81" s="15"/>
-      <c r="AU81" s="15"/>
-      <c r="AV81" s="15"/>
-      <c r="AW81" s="15"/>
-      <c r="AX81" s="15"/>
-      <c r="AY81" s="15"/>
-      <c r="AZ81" s="15"/>
-      <c r="BA81" s="15"/>
-      <c r="BB81" s="15"/>
-      <c r="BC81" s="15"/>
-      <c r="BD81" s="15"/>
-      <c r="BE81" s="15"/>
-      <c r="BF81" s="15"/>
-      <c r="BG81" s="15"/>
-      <c r="BH81" s="15"/>
-      <c r="BI81" s="15"/>
-      <c r="BJ81" s="15"/>
-      <c r="BK81" s="15"/>
-      <c r="BL81" s="15"/>
-      <c r="BM81" s="15"/>
-      <c r="BN81" s="15"/>
-      <c r="BO81" s="15"/>
-      <c r="BP81" s="15"/>
-      <c r="BQ81" s="15"/>
-      <c r="BR81" s="15"/>
-      <c r="BS81" s="15"/>
-      <c r="BT81" s="15"/>
-      <c r="BU81" s="15"/>
-      <c r="BV81" s="15"/>
-      <c r="BW81" s="15"/>
-      <c r="BX81" s="15"/>
-      <c r="BY81" s="15"/>
-      <c r="BZ81" s="15"/>
-      <c r="CA81" s="15"/>
-      <c r="CB81" s="15"/>
-      <c r="CC81" s="15"/>
-      <c r="CD81" s="15"/>
-      <c r="CE81" s="15"/>
-      <c r="CF81" s="15"/>
-      <c r="CG81" s="15"/>
-      <c r="CH81" s="15"/>
-      <c r="CI81" s="15"/>
-      <c r="CJ81" s="15"/>
-      <c r="CK81" s="15"/>
-      <c r="CL81" s="15"/>
-      <c r="CM81" s="15"/>
-      <c r="CN81" s="15"/>
-      <c r="CO81" s="15"/>
-      <c r="CP81" s="15"/>
-      <c r="CQ81" s="15"/>
-      <c r="CR81" s="15"/>
-      <c r="CS81" s="15"/>
-      <c r="CT81" s="15"/>
-      <c r="CU81" s="15"/>
-      <c r="CV81" s="15"/>
-      <c r="CW81" s="15"/>
-      <c r="CX81" s="15"/>
-      <c r="CY81" s="15"/>
-      <c r="CZ81" s="15"/>
-      <c r="DA81" s="15"/>
-      <c r="DB81" s="15"/>
-      <c r="DC81" s="15"/>
-      <c r="DD81" s="15"/>
-      <c r="DE81" s="15"/>
-      <c r="DF81" s="15"/>
-      <c r="DG81" s="15"/>
-      <c r="DH81" s="15"/>
-      <c r="DI81" s="15"/>
-      <c r="DJ81" s="15"/>
-      <c r="DK81" s="15"/>
-      <c r="DL81" s="15"/>
-      <c r="DM81" s="15"/>
-    </row>
-    <row r="82" spans="2:117" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B82" s="19" t="s">
-        <v>82</v>
-      </c>
       <c r="C82" s="20">
         <v>0</v>
       </c>
@@ -5394,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="18">
-        <f t="shared" ref="O82:O89" si="12">SUM(C82:N82)</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="P82" s="15"/>
@@ -5500,10 +5840,8 @@
       <c r="DL82" s="15"/>
       <c r="DM82" s="15"/>
     </row>
-    <row r="83" spans="2:117" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B83" s="19" t="s">
-        <v>83</v>
-      </c>
+    <row r="83" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="45"/>
       <c r="C83" s="20">
         <v>0</v>
       </c>
@@ -5541,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="O83" si="37">SUM(C83:N83)</f>
         <v>0</v>
       </c>
       <c r="P83" s="15"/>
@@ -5647,21 +5985,62 @@
       <c r="DL83" s="15"/>
       <c r="DM83" s="15"/>
     </row>
-    <row r="84" spans="2:117" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B84" s="19"/>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="20"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20"/>
-      <c r="J84" s="20"/>
-      <c r="K84" s="20"/>
-      <c r="L84" s="20"/>
-      <c r="M84" s="20"/>
-      <c r="N84" s="20"/>
-      <c r="O84" s="18"/>
+    <row r="84" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C84" s="44">
+        <f>SUM(C77:C83)</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="44">
+        <f t="shared" ref="D84:O84" si="38">SUM(D77:D83)</f>
+        <v>0</v>
+      </c>
+      <c r="E84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="G84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="J84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="K84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="L84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="M84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O84" s="44">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="P84" s="15"/>
       <c r="Q84" s="15"/>
       <c r="R84" s="15"/>
@@ -5765,28 +6144,23 @@
       <c r="DL84" s="15"/>
       <c r="DM84" s="15"/>
     </row>
-    <row r="85" spans="2:117" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="85" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B85" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
-      <c r="J85" s="37"/>
-      <c r="K85" s="37"/>
-      <c r="L85" s="37"/>
-      <c r="M85" s="37"/>
-      <c r="N85" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="O85" s="21">
-        <f>SUM(O86:O89)</f>
-        <v>0</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C85" s="35"/>
+      <c r="D85" s="35"/>
+      <c r="E85" s="35"/>
+      <c r="F85" s="35"/>
+      <c r="G85" s="35"/>
+      <c r="H85" s="35"/>
+      <c r="I85" s="35"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="35"/>
+      <c r="L85" s="35"/>
+      <c r="M85" s="35"/>
+      <c r="N85" s="29"/>
+      <c r="O85" s="21"/>
       <c r="P85" s="15"/>
       <c r="Q85" s="15"/>
       <c r="R85" s="15"/>
@@ -5890,9 +6264,9 @@
       <c r="DL85" s="15"/>
       <c r="DM85" s="15"/>
     </row>
-    <row r="86" spans="2:117" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="86" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B86" s="19" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C86" s="20">
         <v>0</v>
@@ -5931,7 +6305,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="P86" s="15"/>
@@ -6037,9 +6411,9 @@
       <c r="DL86" s="15"/>
       <c r="DM86" s="15"/>
     </row>
-    <row r="87" spans="2:117" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="87" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B87" s="19" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C87" s="20">
         <v>0</v>
@@ -6078,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="P87" s="15"/>
@@ -6184,9 +6558,9 @@
       <c r="DL87" s="15"/>
       <c r="DM87" s="15"/>
     </row>
-    <row r="88" spans="2:117" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="88" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="19" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C88" s="20">
         <v>0</v>
@@ -6225,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="P88" s="15"/>
@@ -6331,10 +6705,8 @@
       <c r="DL88" s="15"/>
       <c r="DM88" s="15"/>
     </row>
-    <row r="89" spans="2:117" s="35" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B89" s="19" t="s">
-        <v>88</v>
-      </c>
+    <row r="89" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="45"/>
       <c r="C89" s="20">
         <v>0</v>
       </c>
@@ -6372,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="O89" si="39">SUM(C89:N89)</f>
         <v>0</v>
       </c>
       <c r="P89" s="15"/>
@@ -6478,127 +6850,821 @@
       <c r="DL89" s="15"/>
       <c r="DM89" s="15"/>
     </row>
-    <row r="90" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B90" s="19" t="s">
+    <row r="90" spans="2:117" s="33" customFormat="1" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90" s="44">
+        <f>SUM(C86:C89)</f>
+        <v>0</v>
+      </c>
+      <c r="D90" s="44">
+        <f t="shared" ref="D90:O90" si="40">SUM(D86:D89)</f>
+        <v>0</v>
+      </c>
+      <c r="E90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="F90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="G90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="H90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="I90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="K90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="L90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="M90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="N90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="O90" s="44">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="P90" s="15"/>
+      <c r="Q90" s="15"/>
+      <c r="R90" s="15"/>
+      <c r="S90" s="15"/>
+      <c r="T90" s="15"/>
+      <c r="U90" s="15"/>
+      <c r="V90" s="15"/>
+      <c r="W90" s="15"/>
+      <c r="X90" s="15"/>
+      <c r="Y90" s="15"/>
+      <c r="Z90" s="15"/>
+      <c r="AA90" s="15"/>
+      <c r="AB90" s="15"/>
+      <c r="AC90" s="15"/>
+      <c r="AD90" s="15"/>
+      <c r="AE90" s="15"/>
+      <c r="AF90" s="15"/>
+      <c r="AG90" s="15"/>
+      <c r="AH90" s="15"/>
+      <c r="AI90" s="15"/>
+      <c r="AJ90" s="15"/>
+      <c r="AK90" s="15"/>
+      <c r="AL90" s="15"/>
+      <c r="AM90" s="15"/>
+      <c r="AN90" s="15"/>
+      <c r="AO90" s="15"/>
+      <c r="AP90" s="15"/>
+      <c r="AQ90" s="15"/>
+      <c r="AR90" s="15"/>
+      <c r="AS90" s="15"/>
+      <c r="AT90" s="15"/>
+      <c r="AU90" s="15"/>
+      <c r="AV90" s="15"/>
+      <c r="AW90" s="15"/>
+      <c r="AX90" s="15"/>
+      <c r="AY90" s="15"/>
+      <c r="AZ90" s="15"/>
+      <c r="BA90" s="15"/>
+      <c r="BB90" s="15"/>
+      <c r="BC90" s="15"/>
+      <c r="BD90" s="15"/>
+      <c r="BE90" s="15"/>
+      <c r="BF90" s="15"/>
+      <c r="BG90" s="15"/>
+      <c r="BH90" s="15"/>
+      <c r="BI90" s="15"/>
+      <c r="BJ90" s="15"/>
+      <c r="BK90" s="15"/>
+      <c r="BL90" s="15"/>
+      <c r="BM90" s="15"/>
+      <c r="BN90" s="15"/>
+      <c r="BO90" s="15"/>
+      <c r="BP90" s="15"/>
+      <c r="BQ90" s="15"/>
+      <c r="BR90" s="15"/>
+      <c r="BS90" s="15"/>
+      <c r="BT90" s="15"/>
+      <c r="BU90" s="15"/>
+      <c r="BV90" s="15"/>
+      <c r="BW90" s="15"/>
+      <c r="BX90" s="15"/>
+      <c r="BY90" s="15"/>
+      <c r="BZ90" s="15"/>
+      <c r="CA90" s="15"/>
+      <c r="CB90" s="15"/>
+      <c r="CC90" s="15"/>
+      <c r="CD90" s="15"/>
+      <c r="CE90" s="15"/>
+      <c r="CF90" s="15"/>
+      <c r="CG90" s="15"/>
+      <c r="CH90" s="15"/>
+      <c r="CI90" s="15"/>
+      <c r="CJ90" s="15"/>
+      <c r="CK90" s="15"/>
+      <c r="CL90" s="15"/>
+      <c r="CM90" s="15"/>
+      <c r="CN90" s="15"/>
+      <c r="CO90" s="15"/>
+      <c r="CP90" s="15"/>
+      <c r="CQ90" s="15"/>
+      <c r="CR90" s="15"/>
+      <c r="CS90" s="15"/>
+      <c r="CT90" s="15"/>
+      <c r="CU90" s="15"/>
+      <c r="CV90" s="15"/>
+      <c r="CW90" s="15"/>
+      <c r="CX90" s="15"/>
+      <c r="CY90" s="15"/>
+      <c r="CZ90" s="15"/>
+      <c r="DA90" s="15"/>
+      <c r="DB90" s="15"/>
+      <c r="DC90" s="15"/>
+      <c r="DD90" s="15"/>
+      <c r="DE90" s="15"/>
+      <c r="DF90" s="15"/>
+      <c r="DG90" s="15"/>
+      <c r="DH90" s="15"/>
+      <c r="DI90" s="15"/>
+      <c r="DJ90" s="15"/>
+      <c r="DK90" s="15"/>
+      <c r="DL90" s="15"/>
+      <c r="DM90" s="15"/>
+    </row>
+    <row r="91" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="34"/>
+      <c r="D91" s="34"/>
+      <c r="E91" s="34"/>
+      <c r="F91" s="34"/>
+      <c r="G91" s="34"/>
+      <c r="H91" s="34"/>
+      <c r="I91" s="34"/>
+      <c r="J91" s="34"/>
+      <c r="K91" s="34"/>
+      <c r="L91" s="34"/>
+      <c r="M91" s="34"/>
+      <c r="N91" s="29"/>
+      <c r="O91" s="21"/>
+    </row>
+    <row r="92" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C92" s="20">
+        <v>0</v>
+      </c>
+      <c r="D92" s="20">
+        <v>0</v>
+      </c>
+      <c r="E92" s="20">
+        <v>0</v>
+      </c>
+      <c r="F92" s="20">
+        <v>0</v>
+      </c>
+      <c r="G92" s="20">
+        <v>0</v>
+      </c>
+      <c r="H92" s="20">
+        <v>0</v>
+      </c>
+      <c r="I92" s="20">
+        <v>0</v>
+      </c>
+      <c r="J92" s="20">
+        <v>0</v>
+      </c>
+      <c r="K92" s="20">
+        <v>0</v>
+      </c>
+      <c r="L92" s="20">
+        <v>0</v>
+      </c>
+      <c r="M92" s="20">
+        <v>0</v>
+      </c>
+      <c r="N92" s="20">
+        <v>0</v>
+      </c>
+      <c r="O92" s="18">
+        <f t="shared" ref="O92" si="41">SUM(C92:N92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:117" s="15" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C93" s="20">
+        <v>0</v>
+      </c>
+      <c r="D93" s="20">
+        <v>0</v>
+      </c>
+      <c r="E93" s="20">
+        <v>0</v>
+      </c>
+      <c r="F93" s="20">
+        <v>0</v>
+      </c>
+      <c r="G93" s="20">
+        <v>0</v>
+      </c>
+      <c r="H93" s="20">
+        <v>0</v>
+      </c>
+      <c r="I93" s="20">
+        <v>0</v>
+      </c>
+      <c r="J93" s="20">
+        <v>0</v>
+      </c>
+      <c r="K93" s="20">
+        <v>0</v>
+      </c>
+      <c r="L93" s="20">
+        <v>0</v>
+      </c>
+      <c r="M93" s="20">
+        <v>0</v>
+      </c>
+      <c r="N93" s="20">
+        <v>0</v>
+      </c>
+      <c r="O93" s="18">
+        <f t="shared" ref="O93:O101" si="42">SUM(C93:N93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:117" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C94" s="20">
+        <v>0</v>
+      </c>
+      <c r="D94" s="20">
+        <v>0</v>
+      </c>
+      <c r="E94" s="20">
+        <v>0</v>
+      </c>
+      <c r="F94" s="20">
+        <v>0</v>
+      </c>
+      <c r="G94" s="20">
+        <v>0</v>
+      </c>
+      <c r="H94" s="20">
+        <v>0</v>
+      </c>
+      <c r="I94" s="20">
+        <v>0</v>
+      </c>
+      <c r="J94" s="20">
+        <v>0</v>
+      </c>
+      <c r="K94" s="20">
+        <v>0</v>
+      </c>
+      <c r="L94" s="20">
+        <v>0</v>
+      </c>
+      <c r="M94" s="20">
+        <v>0</v>
+      </c>
+      <c r="N94" s="20">
+        <v>0</v>
+      </c>
+      <c r="O94" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:117" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="45"/>
+      <c r="C95" s="20">
+        <v>0</v>
+      </c>
+      <c r="D95" s="20">
+        <v>0</v>
+      </c>
+      <c r="E95" s="20">
+        <v>0</v>
+      </c>
+      <c r="F95" s="20">
+        <v>0</v>
+      </c>
+      <c r="G95" s="20">
+        <v>0</v>
+      </c>
+      <c r="H95" s="20">
+        <v>0</v>
+      </c>
+      <c r="I95" s="20">
+        <v>0</v>
+      </c>
+      <c r="J95" s="20">
+        <v>0</v>
+      </c>
+      <c r="K95" s="20">
+        <v>0</v>
+      </c>
+      <c r="L95" s="20">
+        <v>0</v>
+      </c>
+      <c r="M95" s="20">
+        <v>0</v>
+      </c>
+      <c r="N95" s="20">
+        <v>0</v>
+      </c>
+      <c r="O95" s="18">
+        <f t="shared" ref="O95" si="43">SUM(C95:N95)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:117" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C96" s="44">
+        <f>SUM(C92:C95)</f>
+        <v>0</v>
+      </c>
+      <c r="D96" s="44">
+        <f t="shared" ref="D96:O96" si="44">SUM(D92:D95)</f>
+        <v>0</v>
+      </c>
+      <c r="E96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="F96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="G96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="H96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="I96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="J96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="K96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O96" s="44">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C97" s="35"/>
+      <c r="D97" s="35"/>
+      <c r="E97" s="35"/>
+      <c r="F97" s="35"/>
+      <c r="G97" s="35"/>
+      <c r="H97" s="35"/>
+      <c r="I97" s="35"/>
+      <c r="J97" s="35"/>
+      <c r="K97" s="35"/>
+      <c r="L97" s="35"/>
+      <c r="M97" s="35"/>
+      <c r="N97" s="29"/>
+      <c r="O97" s="21"/>
+    </row>
+    <row r="98" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C98" s="20">
+        <v>0</v>
+      </c>
+      <c r="D98" s="20">
+        <v>0</v>
+      </c>
+      <c r="E98" s="20">
+        <v>0</v>
+      </c>
+      <c r="F98" s="20">
+        <v>0</v>
+      </c>
+      <c r="G98" s="20">
+        <v>0</v>
+      </c>
+      <c r="H98" s="20">
+        <v>0</v>
+      </c>
+      <c r="I98" s="20">
+        <v>0</v>
+      </c>
+      <c r="J98" s="20">
+        <v>0</v>
+      </c>
+      <c r="K98" s="20">
+        <v>0</v>
+      </c>
+      <c r="L98" s="20">
+        <v>0</v>
+      </c>
+      <c r="M98" s="20">
+        <v>0</v>
+      </c>
+      <c r="N98" s="20">
+        <v>0</v>
+      </c>
+      <c r="O98" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C99" s="20">
+        <v>0</v>
+      </c>
+      <c r="D99" s="20">
+        <v>0</v>
+      </c>
+      <c r="E99" s="20">
+        <v>0</v>
+      </c>
+      <c r="F99" s="20">
+        <v>0</v>
+      </c>
+      <c r="G99" s="20">
+        <v>0</v>
+      </c>
+      <c r="H99" s="20">
+        <v>0</v>
+      </c>
+      <c r="I99" s="20">
+        <v>0</v>
+      </c>
+      <c r="J99" s="20">
+        <v>0</v>
+      </c>
+      <c r="K99" s="20">
+        <v>0</v>
+      </c>
+      <c r="L99" s="20">
+        <v>0</v>
+      </c>
+      <c r="M99" s="20">
+        <v>0</v>
+      </c>
+      <c r="N99" s="20">
+        <v>0</v>
+      </c>
+      <c r="O99" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C100" s="20">
+        <v>0</v>
+      </c>
+      <c r="D100" s="20">
+        <v>0</v>
+      </c>
+      <c r="E100" s="20">
+        <v>0</v>
+      </c>
+      <c r="F100" s="20">
+        <v>0</v>
+      </c>
+      <c r="G100" s="20">
+        <v>0</v>
+      </c>
+      <c r="H100" s="20">
+        <v>0</v>
+      </c>
+      <c r="I100" s="20">
+        <v>0</v>
+      </c>
+      <c r="J100" s="20">
+        <v>0</v>
+      </c>
+      <c r="K100" s="20">
+        <v>0</v>
+      </c>
+      <c r="L100" s="20">
+        <v>0</v>
+      </c>
+      <c r="M100" s="20">
+        <v>0</v>
+      </c>
+      <c r="N100" s="20">
+        <v>0</v>
+      </c>
+      <c r="O100" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B101" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C101" s="20">
+        <v>0</v>
+      </c>
+      <c r="D101" s="20">
+        <v>0</v>
+      </c>
+      <c r="E101" s="20">
+        <v>0</v>
+      </c>
+      <c r="F101" s="20">
+        <v>0</v>
+      </c>
+      <c r="G101" s="20">
+        <v>0</v>
+      </c>
+      <c r="H101" s="20">
+        <v>0</v>
+      </c>
+      <c r="I101" s="20">
+        <v>0</v>
+      </c>
+      <c r="J101" s="20">
+        <v>0</v>
+      </c>
+      <c r="K101" s="20">
+        <v>0</v>
+      </c>
+      <c r="L101" s="20">
+        <v>0</v>
+      </c>
+      <c r="M101" s="20">
+        <v>0</v>
+      </c>
+      <c r="N101" s="20">
+        <v>0</v>
+      </c>
+      <c r="O101" s="18">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B102" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C102" s="20">
+        <v>0</v>
+      </c>
+      <c r="D102" s="20">
+        <v>0</v>
+      </c>
+      <c r="E102" s="20">
+        <v>0</v>
+      </c>
+      <c r="F102" s="20">
+        <v>0</v>
+      </c>
+      <c r="G102" s="20">
+        <v>0</v>
+      </c>
+      <c r="H102" s="20">
+        <v>0</v>
+      </c>
+      <c r="I102" s="20">
+        <v>0</v>
+      </c>
+      <c r="J102" s="20">
+        <v>0</v>
+      </c>
+      <c r="K102" s="20">
+        <v>0</v>
+      </c>
+      <c r="L102" s="20">
+        <v>0</v>
+      </c>
+      <c r="M102" s="20">
+        <v>0</v>
+      </c>
+      <c r="N102" s="20">
+        <v>0</v>
+      </c>
+      <c r="O102" s="18">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:15" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="45"/>
+      <c r="C103" s="20">
+        <v>0</v>
+      </c>
+      <c r="D103" s="20">
+        <v>0</v>
+      </c>
+      <c r="E103" s="20">
+        <v>0</v>
+      </c>
+      <c r="F103" s="20">
+        <v>0</v>
+      </c>
+      <c r="G103" s="20">
+        <v>0</v>
+      </c>
+      <c r="H103" s="20">
+        <v>0</v>
+      </c>
+      <c r="I103" s="20">
+        <v>0</v>
+      </c>
+      <c r="J103" s="20">
+        <v>0</v>
+      </c>
+      <c r="K103" s="20">
+        <v>0</v>
+      </c>
+      <c r="L103" s="20">
+        <v>0</v>
+      </c>
+      <c r="M103" s="20">
+        <v>0</v>
+      </c>
+      <c r="N103" s="20">
+        <v>0</v>
+      </c>
+      <c r="O103" s="18">
+        <f t="shared" ref="O103" si="45">SUM(C103:N103)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:15" ht="17" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C104" s="44">
+        <f>SUM(C98:C103)</f>
+        <v>0</v>
+      </c>
+      <c r="D104" s="44">
+        <f t="shared" ref="D104" si="46">SUM(D98:D103)</f>
+        <v>0</v>
+      </c>
+      <c r="E104" s="44">
+        <f t="shared" ref="E104" si="47">SUM(E98:E103)</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="44">
+        <f t="shared" ref="F104" si="48">SUM(F98:F103)</f>
+        <v>0</v>
+      </c>
+      <c r="G104" s="44">
+        <f t="shared" ref="G104" si="49">SUM(G98:G103)</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="44">
+        <f t="shared" ref="H104" si="50">SUM(H98:H103)</f>
+        <v>0</v>
+      </c>
+      <c r="I104" s="44">
+        <f t="shared" ref="I104" si="51">SUM(I98:I103)</f>
+        <v>0</v>
+      </c>
+      <c r="J104" s="44">
+        <f t="shared" ref="J104" si="52">SUM(J98:J103)</f>
+        <v>0</v>
+      </c>
+      <c r="K104" s="44">
+        <f t="shared" ref="K104" si="53">SUM(K98:K103)</f>
+        <v>0</v>
+      </c>
+      <c r="L104" s="44">
+        <f t="shared" ref="L104" si="54">SUM(L98:L103)</f>
+        <v>0</v>
+      </c>
+      <c r="M104" s="44">
+        <f t="shared" ref="M104" si="55">SUM(M98:M103)</f>
+        <v>0</v>
+      </c>
+      <c r="N104" s="44">
+        <f t="shared" ref="N104" si="56">SUM(N98:N103)</f>
+        <v>0</v>
+      </c>
+      <c r="O104" s="44">
+        <f t="shared" ref="O104" si="57">SUM(O98:O103)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="B105" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="C90" s="20">
-        <v>0</v>
-      </c>
-      <c r="D90" s="20">
-        <v>0</v>
-      </c>
-      <c r="E90" s="20">
-        <v>0</v>
-      </c>
-      <c r="F90" s="20">
-        <v>0</v>
-      </c>
-      <c r="G90" s="20">
-        <v>0</v>
-      </c>
-      <c r="H90" s="20">
-        <v>0</v>
-      </c>
-      <c r="I90" s="20">
-        <v>0</v>
-      </c>
-      <c r="J90" s="20">
-        <v>0</v>
-      </c>
-      <c r="K90" s="20">
-        <v>0</v>
-      </c>
-      <c r="L90" s="20">
-        <v>0</v>
-      </c>
-      <c r="M90" s="20">
-        <v>0</v>
-      </c>
-      <c r="N90" s="20">
-        <v>0</v>
-      </c>
-      <c r="O90" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="2:117" s="15" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="B91" s="19"/>
-      <c r="C91" s="20"/>
-      <c r="D91" s="20"/>
-      <c r="E91" s="20"/>
-      <c r="F91" s="20"/>
-      <c r="G91" s="20"/>
-      <c r="H91" s="20"/>
-      <c r="I91" s="20"/>
-      <c r="J91" s="20"/>
-      <c r="K91" s="20"/>
-      <c r="L91" s="20"/>
-      <c r="M91" s="20"/>
-      <c r="N91" s="20"/>
-      <c r="O91" s="18"/>
-    </row>
-    <row r="92" spans="2:117" s="15" customFormat="1" ht="35.1" customHeight="1">
-      <c r="B92" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C92" s="10">
-        <f t="shared" ref="C92:N92" si="13">SUM(C32:C91)</f>
-        <v>0</v>
-      </c>
-      <c r="D92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="F92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="J92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="K92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N92" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="O92" s="43">
+      <c r="C105" s="10">
+        <f>SUM(C37:C41,C44:C48,C51:C61,C64:C67,C70:C74,C77:C83,C86:C89,C92:C95,C98:C103)</f>
+        <v>0</v>
+      </c>
+      <c r="D105" s="10">
+        <f t="shared" ref="D105:M105" si="58">SUM(D37:D41,D44:D48,D51:D61,D64:D67,D70:D74,D77:D83,D86:D89,D92:D95,D98:D103)</f>
+        <v>0</v>
+      </c>
+      <c r="E105" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="G105" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H105" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="I105" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="J105" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="K105" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="L105" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="10">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="N105" s="10">
+        <f>SUM(N37:N41,N44:N48,N51:N61,N64:N67,N70:N74,N77:N83,N86:N89,N92:N95,N98:N103)</f>
+        <v>0</v>
+      </c>
+      <c r="O105" s="41">
         <f>SUM(outcomes[[#This Row],[Janvier]:[Déc]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:5">
-      <c r="B98" s="25"/>
-      <c r="E98" s="2"/>
+    <row r="111" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B111" s="25"/>
+      <c r="E111" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6612,9 +7678,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100668883340522464AA753139DE61DFBF4" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4184e77cb73992caa9a76c50e31ad1a5">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a0aec67c-13da-4bd3-bf62-07b4602bf127" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89bb83f0351a06b8b6a2a97efaea3038" ns2:_="">
-    <xsd:import namespace="a0aec67c-13da-4bd3-bf62-07b4602bf127"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d0c3f830-cbab-496c-8f0c-6aa244f81dd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D8CC7E5D8C7F6B4E9C91972CAFAEB4E7" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b46d8005feeca84e0b112a99a0b8f397">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe" xmlns:ns3="d0c3f830-cbab-496c-8f0c-6aa244f81dd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="76ce2a396ed138893fb1228542f732a5" ns2:_="" ns3:_="">
+    <xsd:import namespace="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe"/>
+    <xsd:import namespace="d0c3f830-cbab-496c-8f0c-6aa244f81dd7"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -6624,6 +7702,14 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -6631,7 +7717,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a0aec67c-13da-4bd3-bf62-07b4602bf127" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -6648,6 +7734,60 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="33941350-b5ef-4818-a0e5-cb5605a3d307" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0c3f830-cbab-496c-8f0c-6aa244f81dd7" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{357b441e-d6c7-4404-a47c-0a66b3c72bc7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0c3f830-cbab-496c-8f0c-6aa244f81dd7">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -6749,12 +7889,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6765,13 +7899,30 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3F675B1-F4FE-4133-9BC0-FB32C00F47A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C8D831E-4A68-43BB-8A70-37E067820D34}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="d0c3f830-cbab-496c-8f0c-6aa244f81dd7"/>
+    <ds:schemaRef ds:uri="be2f80da-0e9f-454a-8f7a-6b0d69f4bcbe"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C8D831E-4A68-43BB-8A70-37E067820D34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11FE7C55-1812-4DC0-AB73-7082219D630D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF5442E9-F47E-455A-9E32-A74D6623B3F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF5442E9-F47E-455A-9E32-A74D6623B3F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>